--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orange_Cap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purple_Cap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Orange_Cap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Purple_Cap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -655,16 +655,16 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>175.86</v>
+        <v>305.88</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -673,7 +673,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -683,16 +683,16 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>238.89</v>
+        <v>175.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -701,7 +701,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -711,16 +711,16 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>217.65</v>
+        <v>238.89</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -729,7 +729,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -739,16 +739,16 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>157.14</v>
+        <v>119.44</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -757,7 +757,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
-        <v>140.91</v>
+        <v>105.56</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -785,7 +785,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -795,16 +795,16 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
-        <v>258.33</v>
+        <v>217.65</v>
       </c>
       <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -813,7 +813,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -823,10 +823,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>142.86</v>
+        <v>157.14</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
@@ -841,7 +841,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -851,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F15" t="n">
-        <v>180</v>
+        <v>140.91</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -879,16 +879,16 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
-        <v>163.64</v>
+        <v>258.33</v>
       </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
         <v>3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -897,7 +897,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -907,13 +907,13 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>200</v>
+        <v>142.86</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -925,7 +925,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -935,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -953,7 +953,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -963,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>122.22</v>
+        <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -991,16 +991,16 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>150</v>
+        <v>163.64</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1019,16 +1019,16 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>114.29</v>
+        <v>120</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1047,13 +1047,13 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F22" t="n">
-        <v>87.5</v>
+        <v>141.67</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1075,13 +1075,13 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1103,16 +1103,16 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1131,16 +1131,16 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
-        <v>133.33</v>
+        <v>127.27</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1159,13 +1159,13 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>100</v>
+        <v>122.22</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1187,16 +1187,16 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1205,25 +1205,417 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>Philip Salt</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Abhishek Sharma</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Anshul Kamboj</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>70</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>David Payne</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>120</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ruturaj Gaikwad</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sanju Samson</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Shivam Dube</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>150</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Naman Dhir</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>250</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jaydev Unadkat</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ramandeep Singh</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Harsh Dubey</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Matt Short</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Nitish Kumar Reddy</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
         <v>16.67</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1238,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,7 +1751,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1369,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -1384,7 +1776,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1394,10 +1786,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1409,7 +1801,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1419,10 +1811,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1434,7 +1826,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1447,7 +1839,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1459,7 +1851,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1472,7 +1864,7 @@
         <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1484,7 +1876,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1494,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1509,7 +1901,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1534,7 +1926,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1544,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1559,7 +1951,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1569,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1584,22 +1976,197 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jaydev Unadkat</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sunil Narine</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kartik Tyagi</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Harsh Dubey</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Abhinandan Singh</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hardik Pandya</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Vaibhav Arora</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
         <v>24</v>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Orange_Cap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Purple_Cap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orange_Cap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purple_Cap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orange_Cap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purple_Cap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Orange_Cap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Purple_Cap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,7 +561,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -571,10 +571,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>181.58</v>
+        <v>163.64</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
@@ -589,7 +589,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -599,13 +599,13 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>167.5</v>
+        <v>181.58</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -617,7 +617,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -627,16 +627,16 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>234.62</v>
+        <v>167.5</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -655,16 +655,16 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>305.88</v>
+        <v>234.62</v>
       </c>
       <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
         <v>4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -673,7 +673,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -683,16 +683,16 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>175.86</v>
+        <v>305.88</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -701,7 +701,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -711,16 +711,16 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>238.89</v>
+        <v>175.86</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -729,7 +729,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -742,13 +742,13 @@
         <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>119.44</v>
+        <v>238.89</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -757,7 +757,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -767,16 +767,16 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>105.56</v>
+        <v>119.44</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -785,7 +785,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -795,16 +795,16 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>217.65</v>
+        <v>144.44</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -813,7 +813,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -823,16 +823,16 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>157.14</v>
+        <v>115.15</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -841,7 +841,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -851,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>140.91</v>
+        <v>105.56</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -879,16 +879,16 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>258.33</v>
+        <v>217.65</v>
       </c>
       <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -897,7 +897,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -907,16 +907,16 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>142.86</v>
+        <v>154.17</v>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
         <v>4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -925,7 +925,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -935,16 +935,16 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F18" t="n">
-        <v>180</v>
+        <v>157.14</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -953,7 +953,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -963,16 +963,16 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>200</v>
+        <v>140.91</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -981,7 +981,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -991,16 +991,16 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
-        <v>163.64</v>
+        <v>258.33</v>
       </c>
       <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
         <v>3</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1019,13 +1019,13 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F21" t="n">
-        <v>120</v>
+        <v>147.06</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1047,16 +1047,16 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>141.67</v>
+        <v>142.86</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1075,16 +1075,16 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1103,16 +1103,16 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1131,16 +1131,16 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F25" t="n">
-        <v>127.27</v>
+        <v>163.64</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1159,16 +1159,16 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F26" t="n">
-        <v>122.22</v>
+        <v>120</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1187,16 +1187,16 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>150</v>
+        <v>163.64</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1215,10 +1215,10 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>114.29</v>
+        <v>112.5</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1243,13 +1243,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>87.5</v>
+        <v>141.67</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1327,16 +1327,16 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>54.55</v>
+        <v>127.27</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1355,13 +1355,13 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F33" t="n">
-        <v>85.70999999999999</v>
+        <v>118.18</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1383,16 +1383,16 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F34" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1411,13 +1411,13 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>71.43000000000001</v>
+        <v>122.22</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1439,16 +1439,16 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F36" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1467,16 +1467,16 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>133.33</v>
+        <v>90</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1495,16 +1495,16 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1523,13 +1523,13 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>114.29</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1551,16 +1551,16 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>28.57</v>
+        <v>87.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F41" t="n">
-        <v>16.67</v>
+        <v>70</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1597,25 +1597,445 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>Priyansh Arya</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>David Payne</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>120</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ruturaj Gaikwad</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sanju Samson</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Shivam Dube</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>150</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Naman Dhir</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>250</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Jaydev Unadkat</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ramandeep Singh</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>100</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Shahrukh Khan</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Shashank Singh</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>80</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Harsh Dubey</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>100</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nehal Wadhera</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>50</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Matt Short</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nitish Kumar Reddy</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>Noor Ahmad</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
         <v>11.11</v>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1630,7 +2050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1701,7 +2121,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1726,7 +2146,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1751,7 +2171,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1764,7 +2184,7 @@
         <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1776,7 +2196,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1786,10 +2206,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1801,7 +2221,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1826,7 +2246,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1851,7 +2271,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1861,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1876,7 +2296,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1886,10 +2306,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1901,7 +2321,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1914,7 +2334,7 @@
         <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1926,7 +2346,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1936,10 +2356,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1951,7 +2371,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1961,7 +2381,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1976,7 +2396,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2001,7 +2421,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2026,7 +2446,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2036,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -2051,7 +2471,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2076,7 +2496,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2086,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -2101,7 +2521,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2111,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -2126,7 +2546,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2151,22 +2571,222 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Jaydev Unadkat</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sunil Narine</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ashok Sharma</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>18</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kartik Tyagi</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kagiso Rabada</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>18</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Harsh Dubey</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Abhinandan Singh</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>18</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hardik Pandya</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Vaibhav Arora</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
         <v>24</v>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Orange_Cap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Purple_Cap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orange_Cap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purple_Cap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,32 +442,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Matches</t>
+          <t>MATCHES</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Inns</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Runs</t>
+          <t>RUNS</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>4s</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>6s</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -490,13 +485,10 @@
         <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>188.37</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +510,10 @@
         <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>210.53</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -546,13 +535,10 @@
         <v>78</v>
       </c>
       <c r="F4" t="n">
-        <v>205.26</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -574,13 +560,10 @@
         <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>163.64</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -602,13 +585,10 @@
         <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>181.58</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -630,13 +610,10 @@
         <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>167.5</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -658,13 +635,10 @@
         <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>234.62</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -686,13 +660,10 @@
         <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>305.88</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -714,13 +685,10 @@
         <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>175.86</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -742,13 +710,10 @@
         <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>238.89</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -770,13 +735,10 @@
         <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>119.44</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -798,12 +760,9 @@
         <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>144.44</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -826,13 +785,10 @@
         <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>115.15</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -854,12 +810,9 @@
         <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>105.56</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -882,13 +835,10 @@
         <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>217.65</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -910,13 +860,10 @@
         <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>154.17</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -938,13 +885,10 @@
         <v>33</v>
       </c>
       <c r="F18" t="n">
-        <v>157.14</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -966,13 +910,10 @@
         <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>140.91</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -994,13 +935,10 @@
         <v>31</v>
       </c>
       <c r="F20" t="n">
-        <v>258.33</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1022,13 +960,10 @@
         <v>25</v>
       </c>
       <c r="F21" t="n">
-        <v>147.06</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1050,12 +985,9 @@
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>142.86</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1078,13 +1010,10 @@
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1106,12 +1035,9 @@
         <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1134,13 +1060,10 @@
         <v>18</v>
       </c>
       <c r="F25" t="n">
-        <v>163.64</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1162,13 +1085,10 @@
         <v>18</v>
       </c>
       <c r="F26" t="n">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1190,13 +1110,10 @@
         <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>163.64</v>
+        <v>18</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1218,12 +1135,9 @@
         <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>112.5</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1246,13 +1160,10 @@
         <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>141.67</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1274,12 +1185,9 @@
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1302,12 +1210,9 @@
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1330,12 +1235,9 @@
         <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>127.27</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1358,12 +1260,9 @@
         <v>13</v>
       </c>
       <c r="F33" t="n">
-        <v>118.18</v>
+        <v>13</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1386,13 +1285,10 @@
         <v>11</v>
       </c>
       <c r="F34" t="n">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1414,12 +1310,9 @@
         <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>122.22</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1442,12 +1335,9 @@
         <v>11</v>
       </c>
       <c r="F36" t="n">
-        <v>220</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1470,13 +1360,10 @@
         <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1498,13 +1385,10 @@
         <v>9</v>
       </c>
       <c r="F38" t="n">
-        <v>150</v>
+        <v>9</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1526,12 +1410,9 @@
         <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>114.29</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1554,13 +1435,10 @@
         <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>87.5</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1582,13 +1460,10 @@
         <v>7</v>
       </c>
       <c r="F41" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1610,13 +1485,10 @@
         <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>87.5</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1638,13 +1510,10 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1666,12 +1535,9 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>54.55</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1694,12 +1560,9 @@
         <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>85.70999999999999</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1722,13 +1585,10 @@
         <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1750,12 +1610,9 @@
         <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>71.43000000000001</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,13 +1635,10 @@
         <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1806,13 +1660,10 @@
         <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>133.33</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1834,13 +1685,10 @@
         <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1862,12 +1710,9 @@
         <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>66.67</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1890,12 +1735,9 @@
         <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1918,12 +1760,9 @@
         <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1946,12 +1785,9 @@
         <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1974,12 +1810,9 @@
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>28.57</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2002,12 +1835,9 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>16.67</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2030,12 +1860,984 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>11.11</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" t="n">
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AM Ghazanfar</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Abhinandan Singh</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Anukul Roy</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Arshdeep Singh</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ashok Sharma</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ayush Mhatre</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Bhuvneshwar Kumar</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Blessing Muzarabani</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Brijesh Sharma</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Eshan Malinga</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Harshal Patel</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Jacob Duffy</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Jasprit Bumrah</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Jitesh Sharma</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kagiso Rabada</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kartik Tyagi</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Khaleel Ahmed</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Krunal Pandya</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Marcus Stoinis</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mayank Markande</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mohammed Siraj</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Nandre Burger</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Prasidh Krishna</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Rashid Khan</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ravi Bishnoi</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ravindra Jadeja</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Romario Shepherd</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sandeep Sharma</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Shardul Thakur</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Sherfane Rutherford</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Shimron Hetmyer</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Sunil Narine</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Trent Boult</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Vaibhav Arora</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Yuzvendra Chahal</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2066,22 +2868,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Matches</t>
+          <t>MATCHES</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Inns</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Balls</t>
+          <t>BALLS</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Wkts</t>
+          <t>WKTS</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,7 +572,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -582,10 +582,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -607,13 +607,13 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -622,7 +622,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -632,10 +632,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -657,10 +657,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,10 +682,10 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,10 +707,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,10 +757,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -782,10 +782,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -797,7 +797,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -807,10 +807,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -822,7 +822,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -832,10 +832,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -857,13 +857,13 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -897,7 +897,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -907,10 +907,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,10 +932,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,10 +957,10 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -982,13 +982,13 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,7 +997,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1032,10 +1032,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,13 +1057,13 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1082,10 +1082,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1157,13 +1157,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,10 +1182,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,13 +1207,13 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1232,13 +1232,13 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F32" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,10 +1257,10 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1282,13 +1282,13 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1307,13 +1307,13 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1357,13 +1357,13 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1382,10 +1382,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1407,13 +1407,13 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,10 +1432,10 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1457,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1482,13 +1482,13 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,13 +1507,13 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,13 +1532,13 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1557,10 +1557,10 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,10 +1607,10 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1632,13 +1632,13 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1682,10 +1682,10 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1707,10 +1707,10 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1732,10 +1732,10 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1757,13 +1757,13 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1782,10 +1782,10 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,10 +1807,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1832,10 +1832,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,10 +1857,10 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2007,10 +2007,10 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2022,20 +2022,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2072,20 +2072,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2132,10 +2132,10 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2147,20 +2147,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2197,14 +2197,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -2222,14 +2222,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2322,14 +2322,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2372,14 +2372,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2472,14 +2472,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2522,14 +2522,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2597,14 +2597,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2772,14 +2772,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2822,22 +2822,622 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>Marcus Stoinis</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Mayank Markande</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Mohammed Siraj</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Mohsin Khan</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mukesh Kumar</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Nandre Burger</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Prasidh Krishna</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Prince Yadav</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Rashid Khan</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ravi Bishnoi</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ravindra Jadeja</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Romario Shepherd</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sandeep Sharma</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Shardul Thakur</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Sherfane Rutherford</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Shimron Hetmyer</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Sunil Narine</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>T Natarajan</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Trent Boult</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Vaibhav Arora</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Vipraj Nigam</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2852,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2948,7 +3548,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2973,7 +3573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2983,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -2998,7 +3598,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3023,7 +3623,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3036,7 +3636,7 @@
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3048,7 +3648,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -3058,10 +3658,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -3073,7 +3673,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3098,7 +3698,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3108,7 +3708,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -3123,7 +3723,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3133,7 +3733,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -3148,7 +3748,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3173,7 +3773,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3186,7 +3786,7 @@
         <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -3198,7 +3798,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3208,10 +3808,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -3223,7 +3823,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3236,7 +3836,7 @@
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -3248,7 +3848,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3258,10 +3858,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -3273,7 +3873,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3298,7 +3898,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3308,7 +3908,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -3323,7 +3923,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3333,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -3348,7 +3948,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3373,7 +3973,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3398,7 +3998,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -3408,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -3423,7 +4023,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3433,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -3448,7 +4048,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3473,7 +4073,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3483,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -3498,7 +4098,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3508,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -3523,7 +4123,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3548,7 +4148,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3573,22 +4173,197 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Sunil Narine</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ashok Sharma</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>18</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kartik Tyagi</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kagiso Rabada</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>18</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Harsh Dubey</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Abhinandan Singh</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>18</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hardik Pandya</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>18</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>Vaibhav Arora</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
         <v>24</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -507,10 +507,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -532,13 +532,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -557,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -572,7 +572,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -582,10 +582,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -632,10 +632,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -657,10 +657,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -697,20 +697,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -722,7 +722,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -747,20 +747,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>41.5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,7 +997,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>28.5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1082,10 +1082,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1122,20 +1122,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1157,13 +1157,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1213,7 +1213,7 @@
         <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,10 +1257,10 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1282,10 +1282,10 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1307,13 +1307,13 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1332,10 +1332,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1357,10 +1357,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1382,10 +1382,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,10 +1432,10 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1482,10 +1482,10 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,10 +1507,10 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,13 +1607,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1632,13 +1632,13 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1682,13 +1682,13 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1707,10 +1707,10 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1732,10 +1732,10 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1757,10 +1757,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1782,10 +1782,10 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,10 +1807,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1822,11 +1822,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,10 +1857,10 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,13 +1882,13 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1907,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1957,10 +1957,10 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,20 +1997,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2057,10 +2057,10 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2082,10 +2082,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2107,10 +2107,10 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2132,10 +2132,10 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2157,10 +2157,10 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2232,10 +2232,10 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2347,11 +2347,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -2372,14 +2372,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2422,14 +2422,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2447,14 +2447,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2522,14 +2522,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2597,14 +2597,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -2622,14 +2622,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2697,14 +2697,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2772,14 +2772,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -2847,14 +2847,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2972,14 +2972,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -3022,14 +3022,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3097,14 +3097,14 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3422,22 +3422,47 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>Vipraj Nigam</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>1</v>
-      </c>
-      <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="n">
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3452,7 +3477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3498,20 +3523,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3523,20 +3548,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3548,7 +3573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3573,7 +3598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3583,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -3598,7 +3623,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3623,7 +3648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3633,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -3648,7 +3673,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -3673,7 +3698,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3686,7 +3711,7 @@
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -3698,20 +3723,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3723,7 +3748,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3736,7 +3761,7 @@
         <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3748,7 +3773,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3758,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -3773,7 +3798,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3783,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -3798,7 +3823,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3823,7 +3848,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3848,7 +3873,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3858,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -3873,7 +3898,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3886,7 +3911,7 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -3898,7 +3923,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3908,10 +3933,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3923,20 +3948,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -3948,20 +3973,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3973,20 +3998,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3998,20 +4023,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>24</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -4023,20 +4048,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4048,7 +4073,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4073,7 +4098,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4083,7 +4108,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -4098,7 +4123,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4108,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -4123,7 +4148,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4148,7 +4173,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4173,7 +4198,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4183,7 +4208,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -4198,7 +4223,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4208,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -4223,7 +4248,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4248,7 +4273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4258,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -4273,7 +4298,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4283,7 +4308,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -4298,7 +4323,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4323,17 +4348,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -4348,22 +4373,122 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ashok Sharma</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>18</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kagiso Rabada</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>18</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Abhinandan Singh</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>18</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hardik Pandya</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>18</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -522,20 +522,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -547,20 +547,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -647,20 +647,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>56.5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>48.33</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,10 +757,10 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>41.5</v>
+        <v>46.5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -772,20 +772,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -882,10 +882,10 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
-        <v>37.5</v>
+        <v>41.5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -901,16 +901,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,10 +932,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -947,20 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -972,20 +972,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
-        <v>32.5</v>
+        <v>36.5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -997,20 +997,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1032,10 +1032,10 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>28.5</v>
+        <v>33.5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,13 +1057,13 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>27.5</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,20 +1072,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>32.5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1107,10 +1107,10 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,20 +1147,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>31.67</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1172,20 +1172,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F32" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>24.5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,20 +1272,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>18</v>
+        <v>24.5</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F35" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -1372,20 +1372,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1397,20 +1397,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>22.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1457,10 +1457,10 @@
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>21.33</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F43" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="F44" t="n">
-        <v>12</v>
+        <v>18.33</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F45" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,10 +1607,10 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -1622,20 +1622,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F50" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1757,10 +1757,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,10 +1807,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F55" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1847,20 +1847,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,13 +1882,13 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,13 +1932,13 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2007,10 +2007,10 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F63" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2032,13 +2032,13 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2072,20 +2072,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,20 +2222,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2357,10 +2357,10 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2747,11 +2747,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -2772,14 +2772,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -2797,14 +2797,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -2822,11 +2822,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -2847,11 +2847,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2897,11 +2897,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
@@ -2922,11 +2922,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -2972,14 +2972,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -3072,11 +3072,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3147,11 +3147,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -3172,11 +3172,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -3197,11 +3197,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -3222,11 +3222,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3272,11 +3272,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3397,11 +3397,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -3422,11 +3422,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3447,22 +3447,322 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>Rahul Chahar</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ravi Bishnoi</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Romario Shepherd</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sandeep Sharma</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>2</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Shardul Thakur</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>T Natarajan</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Trent Boult</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Tushar Deshpande</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Vipraj Nigam</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>1</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="n">
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3477,7 +3777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3523,7 +3823,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3533,10 +3833,10 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3548,7 +3848,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3558,10 +3858,10 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3573,20 +3873,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3598,20 +3898,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3623,20 +3923,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3652,16 +3952,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3673,20 +3973,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -3698,20 +3998,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -3723,20 +4023,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3748,20 +4048,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3773,20 +4073,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3798,20 +4098,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -3823,20 +4123,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -3848,20 +4148,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -3873,20 +4173,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -3898,20 +4198,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -3923,20 +4223,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3948,7 +4248,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3958,10 +4258,10 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -3973,20 +4273,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3998,7 +4298,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4008,7 +4308,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
         <v>2</v>
@@ -4023,7 +4323,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4033,7 +4333,7 @@
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -4048,7 +4348,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4058,7 +4358,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -4073,20 +4373,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -4098,20 +4398,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4123,20 +4423,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -4148,20 +4448,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -4173,7 +4473,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4183,10 +4483,10 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -4198,20 +4498,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -4223,20 +4523,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -4248,20 +4548,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4273,20 +4573,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -4298,20 +4598,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -4323,7 +4623,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4333,7 +4633,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -4348,17 +4648,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -4373,17 +4673,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -4398,7 +4698,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4408,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -4423,7 +4723,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4448,17 +4748,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -4473,7 +4773,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4489,6 +4789,356 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Vipraj Nigam</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Washington Sundar</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>19</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Shivang Kumar</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>48</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>18</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Anukul Roy</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>19</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sunil Narine</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>42</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sandeep Sharma</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>34</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mohammed Siraj</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>36</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Xavier Bartlett</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>48</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Riyan Parag</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Digvesh Rathi</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Corbin Bosch</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>19</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Abhinandan Singh</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>18</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Hardik Pandya</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>18</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -532,10 +532,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -557,10 +557,10 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,7 +597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -607,10 +607,10 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -657,13 +657,13 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>56.5</v>
+        <v>68</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,10 +682,10 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="F10" t="n">
-        <v>51.5</v>
+        <v>56.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>55.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="F12" t="n">
-        <v>48.33</v>
+        <v>51.5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,13 +757,13 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>46.5</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,20 +772,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>48.33</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -797,7 +797,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -807,10 +807,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>46.5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -857,13 +857,13 @@
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -882,13 +882,13 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -897,7 +897,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -907,10 +907,10 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>41.5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -922,20 +922,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,10 +957,10 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -972,20 +972,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>36.5</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1007,10 +1007,10 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>37.5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,13 +1057,13 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1082,10 +1082,10 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F26" t="n">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1107,13 +1107,13 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1132,10 +1132,10 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,20 +1147,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F29" t="n">
-        <v>31.67</v>
+        <v>32.5</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1172,20 +1172,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="F32" t="n">
-        <v>26</v>
+        <v>31.67</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,10 +1257,10 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F33" t="n">
-        <v>24.5</v>
+        <v>28</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,20 +1272,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
-        <v>24.5</v>
+        <v>27</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1307,13 +1307,13 @@
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F35" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>24.67</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1382,10 +1382,10 @@
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1407,10 +1407,10 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F40" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F41" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -1472,20 +1472,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F42" t="n">
-        <v>21.33</v>
+        <v>23</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F43" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F44" t="n">
-        <v>18.33</v>
+        <v>22.5</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F45" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="F46" t="n">
-        <v>18</v>
+        <v>21.33</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F47" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F48" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,11 +1647,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
@@ -1663,7 +1663,7 @@
         <v>18</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F52" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F53" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1782,13 +1782,13 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F54" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,13 +1807,13 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1832,13 +1832,13 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>14</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,20 +1847,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,20 +1872,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F58" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F59" t="n">
-        <v>11</v>
+        <v>13.67</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,13 +1932,13 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,10 +1982,10 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,20 +2022,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2057,13 +2057,13 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2082,10 +2082,10 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2107,13 +2107,13 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F67" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F68" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F71" t="n">
-        <v>6.5</v>
+        <v>7.33</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2257,10 +2257,10 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F74" t="n">
         <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F75" t="n">
         <v>6</v>
@@ -2322,17 +2322,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F76" t="n">
         <v>6</v>
@@ -2372,11 +2372,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2422,11 +2422,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
         <v>2</v>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,17 +2547,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2582,10 +2582,10 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,11 +2597,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
@@ -2613,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,11 +2647,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3777,7 +3777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3883,10 +3883,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3898,20 +3898,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3923,17 +3923,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3958,7 +3958,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -3973,17 +3973,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -3998,17 +3998,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -4023,17 +4023,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4058,7 +4058,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -4073,20 +4073,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -4098,20 +4098,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4133,7 +4133,7 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4173,17 +4173,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -4198,17 +4198,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4233,7 +4233,7 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4258,7 +4258,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4308,10 +4308,10 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4333,10 +4333,10 @@
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4358,7 +4358,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4383,7 +4383,7 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4433,7 +4433,7 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4458,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
@@ -4473,17 +4473,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
         <v>2</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4508,7 +4508,7 @@
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
@@ -4523,17 +4523,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F30" t="n">
         <v>2</v>
@@ -4548,17 +4548,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
@@ -4573,11 +4573,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
@@ -4598,14 +4598,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>30</v>
@@ -4623,20 +4623,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -4648,20 +4648,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -4673,20 +4673,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -4698,20 +4698,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4733,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -4748,17 +4748,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4798,14 +4798,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>24</v>
@@ -4823,17 +4823,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -4848,17 +4848,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -4873,17 +4873,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -4898,14 +4898,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>19</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4933,7 +4933,7 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4958,7 +4958,7 @@
         <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4983,7 +4983,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -5008,7 +5008,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -5023,17 +5023,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -5048,17 +5048,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -5073,17 +5073,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -5098,17 +5098,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -5123,22 +5123,97 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>Corbin Bosch</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>19</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Hardik Pandya</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="n">
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
         <v>18</v>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Shivam Dube</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F2" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -507,10 +507,10 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -522,20 +522,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -557,10 +557,10 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,10 +682,10 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>56.5</v>
+        <v>55.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
-        <v>55.5</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -722,7 +722,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -732,13 +732,13 @@
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>48.33</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -772,20 +772,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="F14" t="n">
-        <v>48.33</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -797,7 +797,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -807,13 +807,13 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>46.5</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>41.5</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>40.67</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -882,13 +882,13 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -897,20 +897,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>41.5</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -922,20 +922,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>39.33</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -947,20 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>34.5</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,20 +997,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F23" t="n">
-        <v>37.5</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1032,13 +1032,13 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F24" t="n">
-        <v>34.5</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>32.67</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1082,10 +1082,10 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F26" t="n">
-        <v>33.5</v>
+        <v>32</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="F27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1132,10 +1132,10 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F28" t="n">
-        <v>33</v>
+        <v>31.67</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,20 +1147,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="F29" t="n">
-        <v>32.5</v>
+        <v>31.67</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="F32" t="n">
-        <v>31.67</v>
+        <v>27</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,10 +1257,10 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1282,10 +1282,10 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F35" t="n">
         <v>26</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="F36" t="n">
-        <v>26</v>
+        <v>24.67</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>24.67</v>
+        <v>24.5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1372,20 +1372,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F38" t="n">
-        <v>24.5</v>
+        <v>24.33</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F41" t="n">
-        <v>23</v>
+        <v>23.67</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,14 +1472,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
         <v>46</v>
@@ -1488,7 +1488,7 @@
         <v>23</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,14 +1497,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>23</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,10 +1532,10 @@
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F44" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1557,10 +1557,10 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="F46" t="n">
-        <v>21.33</v>
+        <v>22.5</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F47" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="F48" t="n">
-        <v>18.33</v>
+        <v>21</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F49" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F50" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1713,7 +1713,7 @@
         <v>18</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,14 +1722,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>18</v>
@@ -1747,14 +1747,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
         <v>18</v>
@@ -1763,7 +1763,7 @@
         <v>18</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F57" t="n">
         <v>14</v>
@@ -1872,14 +1872,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
         <v>14</v>
@@ -1888,7 +1888,7 @@
         <v>14</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F59" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="F60" t="n">
-        <v>12</v>
+        <v>13.67</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F62" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -1997,11 +1997,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2032,10 +2032,10 @@
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
         <v>2</v>
@@ -2147,20 +2147,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F70" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F73" t="n">
-        <v>6.5</v>
+        <v>7.33</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2322,14 +2322,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
         <v>12</v>
@@ -2338,7 +2338,7 @@
         <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2357,13 +2357,13 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2382,13 +2382,13 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F79" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2557,10 +2557,10 @@
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -2597,20 +2597,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2847,14 +2847,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2872,14 +2872,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -2897,11 +2897,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
@@ -2922,11 +2922,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2947,14 +2947,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2997,14 +2997,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3022,11 +3022,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -3047,11 +3047,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -3072,11 +3072,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3147,11 +3147,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -3172,14 +3172,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>2</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -3197,11 +3197,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3247,11 +3247,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3422,11 +3422,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3722,14 +3722,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -3747,22 +3747,72 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Vipraj Nigam</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>2</v>
-      </c>
-      <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="n">
+      <c r="C135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3777,7 +3827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3827,16 +3877,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3848,17 +3898,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -3873,11 +3923,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -3898,17 +3948,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -3923,20 +3973,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3948,7 +3998,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3973,17 +4023,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -3998,17 +4048,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -4023,7 +4073,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4033,7 +4083,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -4048,7 +4098,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4073,17 +4123,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -4098,17 +4148,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -4123,7 +4173,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4133,10 +4183,10 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4148,20 +4198,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4173,7 +4223,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4183,7 +4233,7 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
@@ -4198,17 +4248,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -4223,17 +4273,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -4248,17 +4298,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -4273,17 +4323,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -4298,14 +4348,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>48</v>
@@ -4323,7 +4373,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4333,7 +4383,7 @@
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -4348,7 +4398,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4361,7 +4411,7 @@
         <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4373,20 +4423,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -4398,7 +4448,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4408,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4423,7 +4473,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4433,7 +4483,7 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -4448,7 +4498,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4458,7 +4508,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
@@ -4473,7 +4523,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4483,7 +4533,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F28" t="n">
         <v>2</v>
@@ -4498,17 +4548,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
@@ -4523,7 +4573,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4533,7 +4583,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F30" t="n">
         <v>2</v>
@@ -4548,17 +4598,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
@@ -4573,7 +4623,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4598,17 +4648,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
@@ -4623,7 +4673,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4633,7 +4683,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
@@ -4648,14 +4698,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>30</v>
@@ -4673,17 +4723,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -4698,17 +4748,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -4723,20 +4773,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -4748,20 +4798,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -4773,20 +4823,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -4798,20 +4848,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -4823,7 +4873,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4833,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -4848,7 +4898,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4873,14 +4923,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>24</v>
@@ -4898,17 +4948,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -4923,7 +4973,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4933,7 +4983,7 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -4948,14 +4998,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>19</v>
@@ -4973,7 +5023,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4983,7 +5033,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -4998,17 +5048,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
         <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -5023,7 +5073,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -5033,7 +5083,7 @@
         <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -5048,7 +5098,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5058,7 +5108,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -5073,17 +5123,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -5098,17 +5148,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -5123,17 +5173,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -5148,7 +5198,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -5158,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -5173,17 +5223,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -5198,22 +5248,47 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C57" t="n">
-        <v>3</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
         <v>12</v>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -497,20 +497,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -522,20 +522,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -557,13 +557,13 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F5" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>55.5</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>55.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,20 +747,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>48.33</v>
+        <v>54.5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -782,13 +782,13 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -822,7 +822,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -832,13 +832,13 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="F16" t="n">
-        <v>41.5</v>
+        <v>48.33</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -847,7 +847,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -857,13 +857,13 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
-        <v>40.67</v>
+        <v>41.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>40.67</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -897,11 +897,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -922,20 +922,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>39.33</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -947,20 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>39.33</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -982,13 +982,13 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="F22" t="n">
-        <v>34.5</v>
+        <v>38.67</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,10 +1057,10 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" t="n">
-        <v>32.67</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1072,20 +1072,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>32.67</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1107,10 +1107,10 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>32.67</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1132,10 +1132,10 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28" t="n">
-        <v>31.67</v>
+        <v>32</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,13 +1182,13 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="F30" t="n">
-        <v>29</v>
+        <v>31.67</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F32" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>28.67</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1282,10 +1282,10 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F34" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,20 +1322,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="F36" t="n">
-        <v>24.67</v>
+        <v>27</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1357,10 +1357,10 @@
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F37" t="n">
-        <v>24.5</v>
+        <v>26</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="F38" t="n">
-        <v>24.33</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="F39" t="n">
-        <v>24</v>
+        <v>25.67</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>24.67</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>23.67</v>
+        <v>24.5</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1482,13 +1482,13 @@
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F42" t="n">
-        <v>23</v>
+        <v>24.33</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F46" t="n">
-        <v>22.5</v>
+        <v>23.67</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,13 +1607,13 @@
         <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F47" t="n">
-        <v>21.33</v>
+        <v>23</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1622,20 +1622,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1682,10 +1682,10 @@
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F50" t="n">
-        <v>18.33</v>
+        <v>21.33</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F51" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F52" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F53" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,10 +1807,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F55" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1832,13 +1832,13 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F56" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,13 +1857,13 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F57" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,13 +1882,13 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1907,13 +1907,13 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F60" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F61" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,10 +1982,10 @@
         <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F62" t="n">
-        <v>11.33</v>
+        <v>13.67</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2022,20 +2022,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F68" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F70" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F71" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,20 +2222,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F74" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F75" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F78" t="n">
         <v>6</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2397,17 +2397,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F79" t="n">
         <v>6</v>
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2547,11 +2547,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
         <v>2</v>
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,20 +2597,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
         <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2722,17 +2722,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2897,14 +2897,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -2922,11 +2922,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2972,14 +2972,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -2997,14 +2997,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3022,14 +3022,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -3072,11 +3072,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -3122,11 +3122,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -3147,11 +3147,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -3172,14 +3172,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -3197,11 +3197,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -3222,14 +3222,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>2</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -3247,11 +3247,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3322,11 +3322,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3397,14 +3397,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3908,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3923,17 +3923,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -3948,17 +3948,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3983,7 +3983,7 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -3998,20 +3998,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4033,10 +4033,10 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4058,10 +4058,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4083,7 +4083,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -4123,17 +4123,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -4148,17 +4148,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -4173,17 +4173,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4233,10 +4233,10 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -4248,20 +4248,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
@@ -4298,17 +4298,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4333,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4358,7 +4358,7 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -4373,17 +4373,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -4423,17 +4423,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -4448,17 +4448,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4483,10 +4483,10 @@
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -4498,20 +4498,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4533,10 +4533,10 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -4548,17 +4548,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F29" t="n">
         <v>2</v>
@@ -4573,17 +4573,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F30" t="n">
         <v>2</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4608,7 +4608,7 @@
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
         <v>2</v>
@@ -4623,17 +4623,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F32" t="n">
         <v>2</v>
@@ -4673,17 +4673,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
@@ -4698,14 +4698,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>30</v>
@@ -4723,17 +4723,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -4773,17 +4773,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F38" t="n">
         <v>2</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4808,7 +4808,7 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -4823,17 +4823,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
@@ -4848,17 +4848,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -4873,20 +4873,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4908,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4933,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4958,7 +4958,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -4973,17 +4973,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -5023,17 +5023,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -5123,17 +5123,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -657,13 +657,13 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>55.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,10 +707,10 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F11" t="n">
-        <v>55.5</v>
+        <v>54.5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>51.67</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,13 +757,13 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>54.5</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,14 +772,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>49</v>
@@ -788,7 +788,7 @@
         <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -797,7 +797,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -807,13 +807,13 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>48.33</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,7 +822,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -832,13 +832,13 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>48.33</v>
+        <v>42.5</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="F17" t="n">
-        <v>41.5</v>
+        <v>41.33</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>38.67</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,7 +997,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1007,13 +1007,13 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="F23" t="n">
-        <v>34.5</v>
+        <v>38.67</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,13 +1057,13 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,20 +1072,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="F26" t="n">
-        <v>32.67</v>
+        <v>34</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1107,10 +1107,10 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F27" t="n">
-        <v>32.67</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1132,10 +1132,10 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>32.67</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1157,10 +1157,10 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F29" t="n">
-        <v>31.67</v>
+        <v>32.67</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,10 +1182,10 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F30" t="n">
-        <v>31.67</v>
+        <v>32</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,10 +1207,10 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>31.67</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1232,13 +1232,13 @@
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="F32" t="n">
-        <v>29</v>
+        <v>31.67</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,10 +1257,10 @@
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F33" t="n">
-        <v>28.67</v>
+        <v>31</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="F35" t="n">
-        <v>27</v>
+        <v>28.67</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1332,13 +1332,13 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="F36" t="n">
         <v>27</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1357,10 +1357,10 @@
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F38" t="n">
         <v>26</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
-        <v>25.67</v>
+        <v>26</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,10 +1432,10 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F40" t="n">
-        <v>24.67</v>
+        <v>25.67</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="F41" t="n">
-        <v>24.5</v>
+        <v>24.67</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1582,13 +1582,13 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="F46" t="n">
-        <v>23.67</v>
+        <v>23</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="F47" t="n">
         <v>23</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F48" t="n">
         <v>23</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F49" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1707,13 +1707,13 @@
         <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F51" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1757,13 +1757,13 @@
         <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>18.33</v>
+        <v>21</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="F54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F55" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F56" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F57" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,13 +1882,13 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F59" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F60" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F62" t="n">
-        <v>13.67</v>
+        <v>15</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -1997,20 +1997,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F63" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2057,10 +2057,10 @@
         <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F65" t="n">
-        <v>11.33</v>
+        <v>13.67</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2107,13 +2107,13 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F68" t="n">
-        <v>9</v>
+        <v>11.33</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2147,20 +2147,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F70" t="n">
-        <v>8.33</v>
+        <v>11</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2272,20 +2272,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F74" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2332,10 +2332,10 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F76" t="n">
-        <v>6.67</v>
+        <v>7.33</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2347,20 +2347,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F77" t="n">
-        <v>6.5</v>
+        <v>7.33</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,17 +2447,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F81" t="n">
         <v>6</v>
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F84" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F85" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,11 +2572,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
         <v>2</v>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F89" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>2</v>
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
         <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2797,11 +2797,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -2822,11 +2822,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
@@ -2838,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -2847,11 +2847,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2947,14 +2947,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -2972,14 +2972,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -2997,14 +2997,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3022,11 +3022,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -3072,14 +3072,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3122,11 +3122,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3172,11 +3172,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -3197,11 +3197,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -3222,14 +3222,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>2</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -3247,14 +3247,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -3272,11 +3272,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3322,11 +3322,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3372,11 +3372,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3397,14 +3397,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4023,17 +4023,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -4048,17 +4048,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -4073,20 +4073,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4108,10 +4108,10 @@
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4133,7 +4133,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -4148,17 +4148,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -4173,17 +4173,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -4223,17 +4223,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
@@ -4248,17 +4248,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -4273,20 +4273,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -4298,17 +4298,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -4323,17 +4323,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4358,7 +4358,7 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -4373,17 +4373,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4408,7 +4408,7 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4433,7 +4433,7 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4458,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -4473,17 +4473,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>48</v>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4533,7 +4533,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4558,10 +4558,10 @@
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -4573,20 +4573,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -4598,20 +4598,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4623,17 +4623,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
         <v>2</v>
@@ -4648,17 +4648,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4683,7 +4683,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4708,7 +4708,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F35" t="n">
         <v>2</v>
@@ -4723,17 +4723,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4758,7 +4758,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -4773,17 +4773,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F38" t="n">
         <v>2</v>
@@ -4798,17 +4798,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4873,17 +4873,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -4898,20 +4898,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -4923,20 +4923,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -4948,20 +4948,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4973,20 +4973,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -5023,17 +5023,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -5048,17 +5048,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -5083,7 +5083,7 @@
         <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -5098,17 +5098,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -5123,17 +5123,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -5173,14 +5173,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
         <v>30</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -5248,17 +5248,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -5273,22 +5273,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
         <v>12</v>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>2</v>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
         <v>2</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
         <v>3</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
         <v>2</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
         <v>2</v>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="F2" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="F4" t="n">
-        <v>97</v>
+        <v>91.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -572,7 +572,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -582,10 +582,10 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,7 +622,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -632,13 +632,13 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>64.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="F10" t="n">
-        <v>55.5</v>
+        <v>58.67</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -772,14 +772,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>49</v>
@@ -788,7 +788,7 @@
         <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,7 +797,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -807,13 +807,13 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>48.33</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -822,7 +822,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -832,13 +832,13 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="F16" t="n">
-        <v>42.5</v>
+        <v>48.33</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>41.33</v>
+        <v>42.5</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -882,10 +882,10 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F18" t="n">
-        <v>40.67</v>
+        <v>41.67</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>41.33</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,11 +922,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
@@ -947,20 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>39.33</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>39.33</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="F23" t="n">
-        <v>38.67</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>38.67</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F25" t="n">
-        <v>34.5</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F26" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="F27" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1132,10 +1132,10 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F28" t="n">
-        <v>32.67</v>
+        <v>33</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,10 +1182,10 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>32.67</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" t="n">
-        <v>31.67</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="F34" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1307,13 +1307,13 @@
         <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="F35" t="n">
-        <v>28.67</v>
+        <v>29</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,20 +1322,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F36" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>28.67</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F39" t="n">
         <v>26</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="F40" t="n">
-        <v>25.67</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1457,10 +1457,10 @@
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F41" t="n">
-        <v>24.67</v>
+        <v>25.67</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1482,10 +1482,10 @@
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F42" t="n">
-        <v>24.33</v>
+        <v>24.67</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,13 +1507,13 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="F43" t="n">
-        <v>24</v>
+        <v>24.33</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
         <v>24</v>
@@ -1538,7 +1538,7 @@
         <v>24</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1547,11 +1547,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
         <v>2</v>
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="F50" t="n">
-        <v>21.33</v>
+        <v>22</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1732,13 +1732,13 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F52" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1747,11 +1747,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
         <v>3</v>
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F60" t="n">
         <v>18</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F61" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F62" t="n">
         <v>15</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2007,13 +2007,13 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F65" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F66" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="F67" t="n">
-        <v>12</v>
+        <v>13.67</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
         <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F68" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2182,13 +2182,13 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F71" t="n">
-        <v>9</v>
+        <v>11.33</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,20 +2222,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
-        <v>8.33</v>
+        <v>11</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2282,13 +2282,13 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2297,20 +2297,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
-        <v>7.33</v>
+        <v>9</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2357,10 +2357,10 @@
         <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F77" t="n">
-        <v>7.33</v>
+        <v>8.33</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F80" t="n">
-        <v>6.5</v>
+        <v>7.33</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>7.33</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F90" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2707,10 +2707,10 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2782,10 +2782,10 @@
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2847,11 +2847,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -2863,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2897,11 +2897,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -2997,20 +2997,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3022,20 +3022,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3147,14 +3147,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -3172,11 +3172,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -3197,14 +3197,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -3272,11 +3272,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3322,11 +3322,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3497,14 +3497,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3672,11 +3672,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3797,22 +3797,72 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>3</v>
-      </c>
-      <c r="D135" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="n">
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3827,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3880,13 +3930,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3973,17 +4023,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -3998,17 +4048,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4023,17 +4073,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -4048,17 +4098,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -4073,17 +4123,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -4098,17 +4148,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -4123,7 +4173,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4133,10 +4183,10 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -4148,7 +4198,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4158,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -4173,17 +4223,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
@@ -4198,7 +4248,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4208,7 +4258,7 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -4223,7 +4273,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4233,7 +4283,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
@@ -4248,17 +4298,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -4273,17 +4323,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -4298,7 +4348,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4308,10 +4358,10 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -4323,11 +4373,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
@@ -4336,7 +4386,7 @@
         <v>42</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4348,20 +4398,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -4373,17 +4423,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -4398,17 +4448,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -4423,17 +4473,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -4448,17 +4498,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -4473,17 +4523,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -4498,7 +4548,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4508,7 +4558,7 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -4523,17 +4573,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -4548,17 +4598,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -4573,17 +4623,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -4598,17 +4648,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
@@ -4623,20 +4673,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -4648,7 +4698,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4658,10 +4708,10 @@
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -4673,7 +4723,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4683,10 +4733,10 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -4698,7 +4748,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4708,7 +4758,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F35" t="n">
         <v>2</v>
@@ -4723,17 +4773,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -4748,17 +4798,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -4773,7 +4823,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4798,17 +4848,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -4823,7 +4873,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4833,7 +4883,7 @@
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
@@ -4848,7 +4898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4858,7 +4908,7 @@
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -4873,17 +4923,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -4898,17 +4948,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
@@ -4923,17 +4973,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -4948,7 +4998,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4973,7 +5023,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4983,7 +5033,7 @@
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F46" t="n">
         <v>2</v>
@@ -4998,20 +5048,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -5023,20 +5073,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -5048,7 +5098,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -5058,7 +5108,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -5073,17 +5123,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -5098,17 +5148,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -5123,17 +5173,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -5148,17 +5198,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -5173,17 +5223,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -5198,14 +5248,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
         <v>30</v>
@@ -5223,17 +5273,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -5248,17 +5298,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -5273,17 +5323,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -5298,22 +5348,47 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
         <v>12</v>
       </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="n">
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -497,20 +497,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="F3" t="n">
-        <v>99</v>
+        <v>91.5</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>91.5</v>
+        <v>80</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -557,10 +557,10 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="F5" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -572,7 +572,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -582,13 +582,13 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>68.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="F10" t="n">
-        <v>58.67</v>
+        <v>59.5</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="F11" t="n">
-        <v>54.5</v>
+        <v>58.67</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="F12" t="n">
-        <v>51.67</v>
+        <v>54.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,13 +757,13 @@
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>51.67</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -797,14 +797,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>49</v>
@@ -813,7 +813,7 @@
         <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>48.33</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="F17" t="n">
-        <v>42.5</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F18" t="n">
-        <v>41.67</v>
+        <v>43.67</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -897,20 +897,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="F19" t="n">
-        <v>41.33</v>
+        <v>42.5</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -922,20 +922,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>41.67</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>41.33</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -972,20 +972,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="F22" t="n">
-        <v>39.33</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>39.33</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>38.67</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>38.67</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,20 +1072,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F26" t="n">
-        <v>34.5</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F27" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1132,10 +1132,10 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F28" t="n">
-        <v>33</v>
+        <v>34.33</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>32.67</v>
+        <v>34</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1172,20 +1172,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F30" t="n">
-        <v>32.67</v>
+        <v>33</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,10 +1207,10 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>32.67</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1232,10 +1232,10 @@
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F32" t="n">
-        <v>31.67</v>
+        <v>32.67</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="F33" t="n">
-        <v>31</v>
+        <v>32.25</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="F34" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
         <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="F35" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F36" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="F37" t="n">
-        <v>28.67</v>
+        <v>30.5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1372,20 +1372,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F38" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="F39" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F40" t="n">
-        <v>26</v>
+        <v>28.67</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="F41" t="n">
-        <v>25.67</v>
+        <v>27</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1482,10 +1482,10 @@
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F42" t="n">
-        <v>24.67</v>
+        <v>26</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="F43" t="n">
-        <v>24.33</v>
+        <v>26</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,13 +1532,13 @@
         <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="F44" t="n">
-        <v>24</v>
+        <v>25.67</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="F46" t="n">
-        <v>23</v>
+        <v>24.67</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="F47" t="n">
-        <v>23</v>
+        <v>24.33</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1682,13 +1682,13 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1707,10 +1707,10 @@
         <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F51" t="n">
-        <v>21.33</v>
+        <v>22</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="F52" t="n">
-        <v>21.33</v>
+        <v>22</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1747,20 +1747,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F53" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F54" t="n">
-        <v>20</v>
+        <v>21.33</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
-        <v>18.67</v>
+        <v>21</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F56" t="n">
-        <v>18.33</v>
+        <v>20</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F57" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F58" t="n">
         <v>18</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1913,7 +1913,7 @@
         <v>18</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F60" t="n">
         <v>18</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F61" t="n">
         <v>18</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
         <v>2</v>
@@ -2347,20 +2347,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
         <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F77" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F82" t="n">
-        <v>6.67</v>
+        <v>7.33</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F83" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F84" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2572,17 +2572,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F86" t="n">
         <v>6</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,11 +2622,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -2638,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F89" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,11 +2672,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>2</v>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4058,7 +4058,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4073,17 +4073,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4158,7 +4158,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -4173,17 +4173,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -4198,20 +4198,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4283,7 +4283,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
@@ -4298,17 +4298,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4333,7 +4333,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -4348,17 +4348,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -4373,17 +4373,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -4423,20 +4423,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -4448,20 +4448,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4473,17 +4473,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>42</v>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4533,7 +4533,7 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -4548,17 +4548,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -4573,17 +4573,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -4598,11 +4598,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4633,7 +4633,7 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -4698,17 +4698,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F33" t="n">
         <v>3</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -4733,7 +4733,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -4748,20 +4748,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>42</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -4773,17 +4773,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -4798,17 +4798,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="F37" t="n">
         <v>2</v>
@@ -4823,17 +4823,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F38" t="n">
         <v>2</v>
@@ -4848,17 +4848,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4898,17 +4898,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4933,7 +4933,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -4948,17 +4948,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
@@ -4973,17 +4973,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F45" t="n">
         <v>2</v>
@@ -5023,17 +5023,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F46" t="n">
         <v>2</v>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5073,17 +5073,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -5098,20 +5098,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -5123,20 +5123,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5158,10 +5158,10 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -5173,17 +5173,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -5223,17 +5223,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -5248,17 +5248,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -5273,17 +5273,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -5298,17 +5298,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -5323,17 +5323,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -5348,17 +5348,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -5373,11 +5373,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
@@ -5389,6 +5389,56 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Shivam Dube</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>12</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -532,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>59.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="F10" t="n">
-        <v>59.5</v>
+        <v>58.67</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,10 +707,10 @@
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F11" t="n">
-        <v>58.67</v>
+        <v>55.33</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,13 +757,13 @@
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>51.67</v>
+        <v>54.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -782,13 +782,13 @@
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>51.67</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,14 +822,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>49</v>
@@ -838,7 +838,7 @@
         <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>43.67</v>
+        <v>45.67</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F19" t="n">
-        <v>42.5</v>
+        <v>44.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -922,20 +922,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F20" t="n">
-        <v>41.67</v>
+        <v>43.67</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -947,20 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="F21" t="n">
-        <v>41.33</v>
+        <v>42.5</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -972,20 +972,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>41.67</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F23" t="n">
-        <v>39.33</v>
+        <v>41.33</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,10 +1057,10 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F25" t="n">
-        <v>38.67</v>
+        <v>39.33</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1072,20 +1072,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="F26" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="F27" t="n">
-        <v>34.5</v>
+        <v>38.67</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F28" t="n">
-        <v>34.33</v>
+        <v>36</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>34.33</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,13 +1182,13 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F31" t="n">
-        <v>32.67</v>
+        <v>33.25</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F32" t="n">
-        <v>32.67</v>
+        <v>33</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="F33" t="n">
-        <v>32.25</v>
+        <v>32.67</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F34" t="n">
-        <v>32</v>
+        <v>32.67</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,20 +1297,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="F35" t="n">
-        <v>31</v>
+        <v>32.25</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="F36" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1357,10 +1357,10 @@
         <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F37" t="n">
-        <v>30.5</v>
+        <v>31.75</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="F38" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="F39" t="n">
-        <v>29</v>
+        <v>30.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>28.67</v>
+        <v>29</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F41" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -1472,20 +1472,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="F42" t="n">
-        <v>26</v>
+        <v>27.75</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,10 +1532,10 @@
         <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F44" t="n">
-        <v>25.67</v>
+        <v>26</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F46" t="n">
-        <v>24.67</v>
+        <v>25.67</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="F47" t="n">
-        <v>24.33</v>
+        <v>25.5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1632,13 +1632,13 @@
         <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="F48" t="n">
-        <v>24</v>
+        <v>24.33</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,14 +1647,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
         <v>24</v>
@@ -1663,7 +1663,7 @@
         <v>24</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="F51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="F52" t="n">
         <v>22</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="F53" t="n">
-        <v>21.33</v>
+        <v>22</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1772,14 +1772,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
         <v>64</v>
@@ -1788,7 +1788,7 @@
         <v>21.33</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,13 +1807,13 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F55" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,13 +1857,13 @@
         <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F57" t="n">
-        <v>18.67</v>
+        <v>20</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,20 +1872,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F59" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F60" t="n">
         <v>18</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F61" t="n">
         <v>18</v>
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F62" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="F63" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F64" t="n">
         <v>15</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2057,13 +2057,13 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F67" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F68" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -2147,20 +2147,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F69" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
         <v>12</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F71" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,20 +2272,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F74" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2307,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F75" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,14 +2322,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>9</v>
@@ -2347,17 +2347,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F77" t="n">
         <v>9</v>
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F78" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F80" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F81" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2507,10 +2507,10 @@
         <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F83" t="n">
-        <v>6.67</v>
+        <v>7.33</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F84" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F87" t="n">
         <v>6</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,11 +2647,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
@@ -2663,7 +2663,7 @@
         <v>5</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,11 +2697,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2807,10 +2807,10 @@
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2882,10 +2882,10 @@
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -2963,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2972,17 +2972,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
@@ -2997,17 +2997,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -3022,11 +3022,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -3038,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -3063,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3072,20 +3072,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3122,20 +3122,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3157,13 +3157,13 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,11 +3172,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -3197,14 +3197,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3222,11 +3222,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -3247,14 +3247,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -3272,14 +3272,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3322,14 +3322,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3397,11 +3397,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3497,14 +3497,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3647,14 +3647,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3847,22 +3847,147 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>Sandeep Sharma</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Tushar Deshpande</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>4</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>4</v>
-      </c>
-      <c r="D137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G137" t="n">
+      <c r="C142" t="n">
+        <v>4</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3877,7 +4002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3948,20 +4073,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3973,7 +4098,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3986,7 +4111,7 @@
         <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3998,17 +4123,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -4023,7 +4148,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4033,7 +4158,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -4048,7 +4173,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4073,7 +4198,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4083,7 +4208,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -4098,17 +4223,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -4123,17 +4248,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -4148,17 +4273,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -4173,17 +4298,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -4198,7 +4323,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4208,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -4223,7 +4348,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4233,10 +4358,10 @@
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4298,17 +4423,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -4323,7 +4448,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4333,7 +4458,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -4348,7 +4473,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4358,7 +4483,7 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -4373,17 +4498,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -4398,17 +4523,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -4423,17 +4548,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -4448,17 +4573,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
@@ -4473,7 +4598,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4483,10 +4608,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -4498,17 +4623,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -4523,14 +4648,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>42</v>
@@ -4548,17 +4673,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -4573,7 +4698,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4583,7 +4708,7 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -4598,7 +4723,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4608,7 +4733,7 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -4623,17 +4748,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -4648,17 +4773,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
@@ -4673,17 +4798,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -4698,17 +4823,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
         <v>3</v>
@@ -4723,17 +4848,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -4748,17 +4873,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -4773,20 +4898,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -4798,20 +4923,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
         <v>42</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -4823,17 +4948,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F38" t="n">
         <v>2</v>
@@ -4848,17 +4973,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
@@ -4873,17 +4998,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
@@ -4898,17 +5023,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -4923,17 +5048,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -4948,17 +5073,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
@@ -4973,17 +5098,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -4998,17 +5123,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="F45" t="n">
         <v>2</v>
@@ -5023,17 +5148,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="F46" t="n">
         <v>2</v>
@@ -5048,17 +5173,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -5073,7 +5198,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -5098,17 +5223,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -5123,17 +5248,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
@@ -5148,17 +5273,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
@@ -5173,20 +5298,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -5198,7 +5323,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5208,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -5223,17 +5348,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -5248,17 +5373,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -5273,17 +5398,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -5298,17 +5423,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -5323,7 +5448,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5333,7 +5458,7 @@
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -5348,17 +5473,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -5373,17 +5498,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -5398,17 +5523,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -5423,22 +5548,97 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="n">
+        <v>78</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Corbin Bosch</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>19</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>12</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>4</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
         <v>12</v>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>68.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -597,20 +597,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F7" t="n">
-        <v>68.5</v>
+        <v>64.5</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -622,20 +622,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F8" t="n">
-        <v>64.5</v>
+        <v>59.5</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -647,20 +647,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="F9" t="n">
-        <v>59.5</v>
+        <v>58.67</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F10" t="n">
-        <v>58.67</v>
+        <v>55.33</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F11" t="n">
-        <v>55.33</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -722,14 +722,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>109</v>
@@ -738,7 +738,7 @@
         <v>54.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,13 +757,13 @@
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="F13" t="n">
-        <v>54.5</v>
+        <v>51.67</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -782,13 +782,13 @@
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="F14" t="n">
-        <v>51.67</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -847,7 +847,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -857,13 +857,13 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>45.67</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -882,13 +882,13 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
-        <v>45.67</v>
+        <v>44.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -897,7 +897,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -907,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="F19" t="n">
-        <v>44.5</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
-        <v>43.67</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="F21" t="n">
-        <v>42.5</v>
+        <v>43.67</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>38.67</v>
+        <v>36</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
+        <v>34.33</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1147,14 +1147,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
         <v>103</v>
@@ -1163,7 +1163,7 @@
         <v>34.33</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
         <v>34</v>
@@ -1188,7 +1188,7 @@
         <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="F31" t="n">
-        <v>33.25</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="F32" t="n">
-        <v>33</v>
+        <v>33.25</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F33" t="n">
-        <v>32.67</v>
+        <v>33</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1307,13 +1307,13 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="F35" t="n">
-        <v>32.25</v>
+        <v>32.67</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1332,13 +1332,13 @@
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="F36" t="n">
-        <v>32</v>
+        <v>32.25</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1357,13 +1357,13 @@
         <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="F37" t="n">
-        <v>31.75</v>
+        <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>31</v>
+        <v>31.75</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="F39" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="F40" t="n">
-        <v>29</v>
+        <v>30.5</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F41" t="n">
         <v>29</v>
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="F42" t="n">
-        <v>27.75</v>
+        <v>29</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="F43" t="n">
-        <v>27</v>
+        <v>28.25</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="F44" t="n">
-        <v>26</v>
+        <v>27.75</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="F46" t="n">
-        <v>25.67</v>
+        <v>27</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F47" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1622,20 +1622,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="F48" t="n">
-        <v>24.33</v>
+        <v>25.5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1657,13 +1657,13 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="F49" t="n">
-        <v>24</v>
+        <v>24.33</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
         <v>2</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
@@ -1722,17 +1722,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="F52" t="n">
         <v>22</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="F53" t="n">
-        <v>22</v>
+        <v>21.33</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="F54" t="n">
-        <v>21.33</v>
+        <v>21</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F55" t="n">
-        <v>21.33</v>
+        <v>20</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,10 +1857,10 @@
         <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,20 +1872,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="F58" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F60" t="n">
         <v>18</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2047,17 +2047,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F65" t="n">
         <v>15</v>
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
         <v>15</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2122,14 +2122,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>14</v>
@@ -2138,7 +2138,7 @@
         <v>14</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F69" t="n">
         <v>14</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F70" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F71" t="n">
         <v>12</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F73" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F74" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2297,11 +2297,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -2347,20 +2347,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F77" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2372,14 +2372,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>9</v>
@@ -2397,17 +2397,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F79" t="n">
         <v>9</v>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F82" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F85" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F88" t="n">
         <v>6</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F91" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2807,10 +2807,10 @@
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F95" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2872,20 +2872,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F98" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,20 +2922,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F100" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -2997,20 +2997,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>4</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3097,11 +3097,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3122,11 +3122,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
@@ -3138,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3147,11 +3147,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -3163,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3197,11 +3197,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -3222,11 +3222,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -3247,14 +3247,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -3272,11 +3272,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -3297,14 +3297,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>4</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3347,14 +3347,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3397,11 +3397,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -3422,11 +3422,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3647,14 +3647,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3797,11 +3797,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3822,11 +3822,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3922,14 +3922,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3972,22 +3972,47 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>4</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>4</v>
-      </c>
-      <c r="D142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="n">
+      <c r="C143" t="n">
+        <v>4</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4048,7 +4073,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4058,10 +4083,10 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4073,7 +4098,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4083,10 +4108,10 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4098,20 +4123,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4123,20 +4148,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4148,7 +4173,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4158,7 +4183,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -4173,7 +4198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4183,7 +4208,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4198,7 +4223,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4223,7 +4248,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4233,7 +4258,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -4248,17 +4273,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -4373,17 +4398,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -4398,7 +4423,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4423,17 +4448,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -4448,7 +4473,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4458,7 +4483,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -4473,7 +4498,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4483,7 +4508,7 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -4498,7 +4523,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4508,7 +4533,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -4523,17 +4548,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -4548,17 +4573,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -4573,7 +4598,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4583,7 +4608,7 @@
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
@@ -4598,17 +4623,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -4623,20 +4648,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4648,20 +4673,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -4673,20 +4698,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -4698,14 +4723,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>42</v>
@@ -4723,17 +4748,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -4748,7 +4773,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4758,7 +4783,7 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -4773,17 +4798,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
@@ -4798,17 +4823,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -4823,17 +4848,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F33" t="n">
         <v>3</v>
@@ -4848,17 +4873,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -4873,7 +4898,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4883,7 +4908,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -4898,7 +4923,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -4908,7 +4933,7 @@
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -4923,17 +4948,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -4948,20 +4973,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -4973,20 +4998,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -4998,7 +5023,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5008,10 +5033,10 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -5023,17 +5048,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F41" t="n">
         <v>2</v>
@@ -5048,17 +5073,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -5073,17 +5098,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F43" t="n">
         <v>2</v>
@@ -5098,17 +5123,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F44" t="n">
         <v>2</v>
@@ -5123,17 +5148,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F45" t="n">
         <v>2</v>
@@ -5148,7 +5173,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5158,7 +5183,7 @@
         <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F46" t="n">
         <v>2</v>
@@ -5173,17 +5198,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -5198,17 +5223,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -5223,17 +5248,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -5377,7 +5402,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
         <v>2</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -547,20 +547,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
+        <v>68.5</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -572,20 +572,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="F6" t="n">
-        <v>68.5</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="F7" t="n">
-        <v>64.5</v>
+        <v>59.67</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -847,7 +847,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -857,13 +857,13 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="F17" t="n">
-        <v>45.67</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -882,13 +882,13 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>44.5</v>
+        <v>45.67</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,7 +897,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -907,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>45.67</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,10 +932,10 @@
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -947,20 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="F21" t="n">
-        <v>43.67</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="F22" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F23" t="n">
-        <v>41.33</v>
+        <v>43.67</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>41.67</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F25" t="n">
-        <v>39.33</v>
+        <v>41.33</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F28" t="n">
-        <v>34.33</v>
+        <v>36</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1147,14 +1147,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>103</v>
@@ -1163,7 +1163,7 @@
         <v>34.33</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,13 +1182,13 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>34</v>
+        <v>34.33</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
         <v>34</v>
@@ -1213,7 +1213,7 @@
         <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="F32" t="n">
-        <v>33.25</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F33" t="n">
-        <v>33</v>
+        <v>33.75</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1282,13 +1282,13 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="F34" t="n">
-        <v>32.67</v>
+        <v>33.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1307,13 +1307,13 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F35" t="n">
-        <v>32.67</v>
+        <v>33.25</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1332,10 +1332,10 @@
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F36" t="n">
-        <v>32.25</v>
+        <v>33</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F37" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1382,13 +1382,13 @@
         <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="F38" t="n">
-        <v>31.75</v>
+        <v>32.67</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="F39" t="n">
-        <v>31</v>
+        <v>32.25</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,13 +1432,13 @@
         <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="F40" t="n">
-        <v>30.5</v>
+        <v>32</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>31.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,10 +1507,10 @@
         <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F43" t="n">
-        <v>28.25</v>
+        <v>30.5</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="F44" t="n">
-        <v>27.75</v>
+        <v>29</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1557,10 +1557,10 @@
         <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F45" t="n">
-        <v>27</v>
+        <v>28.25</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="F46" t="n">
-        <v>27</v>
+        <v>27.75</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="F47" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1632,10 +1632,10 @@
         <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F48" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
-        <v>24.33</v>
+        <v>26</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
         <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="F51" t="n">
-        <v>23</v>
+        <v>25.5</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1747,20 +1747,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
-        <v>21.33</v>
+        <v>24</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F54" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,13 +1807,13 @@
         <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F55" t="n">
-        <v>20</v>
+        <v>21.33</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,10 +1857,10 @@
         <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F57" t="n">
-        <v>18.75</v>
+        <v>20</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,13 +1882,13 @@
         <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F58" t="n">
-        <v>18.75</v>
+        <v>19.67</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="F59" t="n">
-        <v>18.67</v>
+        <v>19</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,10 +1932,10 @@
         <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F60" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F61" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F62" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -1997,17 +1997,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F63" t="n">
         <v>18</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2032,10 +2032,10 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2072,17 +2072,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F66" t="n">
         <v>15</v>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
         <v>15</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F74" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2297,11 +2297,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F76" t="n">
-        <v>11</v>
+        <v>10.25</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="F77" t="n">
-        <v>10.25</v>
+        <v>9</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2372,11 +2372,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         <v>9</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2397,14 +2397,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>9</v>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F80" t="n">
         <v>9</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F81" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2747,17 +2747,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
         <v>5</v>
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2797,11 +2797,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
         <v>2</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,11 +2847,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -2863,7 +2863,7 @@
         <v>4</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F98" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,20 +2922,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F100" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3997,22 +3997,47 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>4</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C143" t="n">
-        <v>4</v>
-      </c>
-      <c r="D143" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="n">
+      <c r="C144" t="n">
+        <v>4</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4027,7 +4052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4173,20 +4198,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4198,7 +4223,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4208,7 +4233,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -4223,7 +4248,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4233,7 +4258,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -4248,7 +4273,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4273,7 +4298,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4283,7 +4308,7 @@
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -4298,17 +4323,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -4323,17 +4348,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -4348,17 +4373,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -4373,7 +4398,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4383,7 +4408,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -4398,20 +4423,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4423,20 +4448,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -4448,17 +4473,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -4473,17 +4498,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -4498,17 +4523,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -4523,7 +4548,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4533,7 +4558,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -4548,7 +4573,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4558,7 +4583,7 @@
         <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -4573,17 +4598,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -4598,7 +4623,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4608,7 +4633,7 @@
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
@@ -4623,17 +4648,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -4648,7 +4673,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4658,7 +4683,7 @@
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
@@ -4673,17 +4698,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -4698,17 +4723,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
@@ -4723,20 +4748,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -4748,17 +4773,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F29" t="n">
         <v>3</v>
@@ -4773,17 +4798,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="F30" t="n">
         <v>3</v>
@@ -4798,7 +4823,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4808,7 +4833,7 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
@@ -4823,17 +4848,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -4848,17 +4873,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="F33" t="n">
         <v>3</v>
@@ -4873,17 +4898,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -4898,7 +4923,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -4908,7 +4933,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -4923,17 +4948,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -4948,17 +4973,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -4973,14 +4998,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>66</v>
@@ -4998,17 +5023,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -5023,7 +5048,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5033,7 +5058,7 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -5048,20 +5073,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -5073,17 +5098,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F42" t="n">
         <v>2</v>
@@ -5173,14 +5198,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>42</v>
@@ -5198,17 +5223,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -5223,17 +5248,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -5248,17 +5273,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -5273,17 +5298,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
@@ -5298,17 +5323,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
@@ -5323,7 +5348,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5333,7 +5358,7 @@
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
@@ -5348,20 +5373,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -5373,20 +5398,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -5398,17 +5423,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -5423,17 +5448,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -5448,17 +5473,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -5473,17 +5498,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -5498,17 +5523,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -5523,17 +5548,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -5548,17 +5573,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -5573,17 +5598,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -5598,17 +5623,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -5623,17 +5648,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -5648,22 +5673,72 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>Corbin Bosch</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>19</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>12</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>4</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="n">
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
         <v>12</v>
       </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,20 +497,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>91.5</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -522,20 +522,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F7" t="n">
-        <v>59.67</v>
+        <v>61.33</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,20 +622,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="F8" t="n">
-        <v>59.5</v>
+        <v>59.67</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -647,20 +647,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="F9" t="n">
-        <v>58.67</v>
+        <v>59.5</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>45.67</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -857,13 +857,13 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>45.67</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>137</v>
+        <v>224</v>
       </c>
       <c r="F18" t="n">
-        <v>45.67</v>
+        <v>44.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -897,7 +897,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -907,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="F19" t="n">
-        <v>45.67</v>
+        <v>44.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="F20" t="n">
-        <v>44.5</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="F24" t="n">
-        <v>41.67</v>
+        <v>42.6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F25" t="n">
-        <v>41.33</v>
+        <v>41.67</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>41.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F29" t="n">
-        <v>34.33</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1172,20 +1172,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F30" t="n">
-        <v>34.33</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F31" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="F32" t="n">
-        <v>34</v>
+        <v>34.33</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,13 +1257,13 @@
         <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="F33" t="n">
-        <v>33.75</v>
+        <v>34.33</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F34" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="F35" t="n">
-        <v>33.25</v>
+        <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1332,10 +1332,10 @@
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F36" t="n">
-        <v>33</v>
+        <v>33.75</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="F37" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1382,13 +1382,13 @@
         <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F38" t="n">
-        <v>32.67</v>
+        <v>33.25</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1407,10 +1407,10 @@
         <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F39" t="n">
-        <v>32.25</v>
+        <v>33</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F40" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1457,13 +1457,13 @@
         <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="F41" t="n">
-        <v>31.75</v>
+        <v>32.67</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="F42" t="n">
-        <v>31</v>
+        <v>31.75</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F43" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F51" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F54" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="F55" t="n">
-        <v>21.33</v>
+        <v>24</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,13 +1882,13 @@
         <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="F58" t="n">
-        <v>19.67</v>
+        <v>20</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F59" t="n">
-        <v>19</v>
+        <v>19.67</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="F60" t="n">
-        <v>18.75</v>
+        <v>19</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,13 +1982,13 @@
         <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F62" t="n">
-        <v>18.67</v>
+        <v>18.75</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2007,13 +2007,13 @@
         <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F63" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="F64" t="n">
         <v>18</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2057,10 +2057,10 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F65" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2072,20 +2072,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F66" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2107,13 +2107,13 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2132,13 +2132,13 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2147,14 +2147,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>14</v>
@@ -2163,7 +2163,7 @@
         <v>14</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F70" t="n">
         <v>14</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F71" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="F73" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2272,20 +2272,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="F76" t="n">
-        <v>10.25</v>
+        <v>12</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2347,20 +2347,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F77" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2382,13 +2382,13 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F78" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F79" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F80" t="n">
         <v>9</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>4</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F84" t="n">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F85" t="n">
-        <v>7</v>
+        <v>8.33</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F86" t="n">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
         <v>5</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2788,7 +2788,7 @@
         <v>5</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F96" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F97" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F99" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2932,13 +2932,13 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F101" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2997,20 +2997,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
         <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,20 +3047,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3097,20 +3097,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>4</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3147,11 +3147,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3197,20 +3197,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3247,11 +3247,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -3272,14 +3272,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
@@ -3297,14 +3297,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3372,11 +3372,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3397,14 +3397,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3422,11 +3422,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3647,14 +3647,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3797,11 +3797,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -4022,22 +4022,97 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>4</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C144" t="n">
-        <v>4</v>
-      </c>
-      <c r="D144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="n">
+      <c r="C147" t="n">
+        <v>4</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4052,7 +4127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4127,13 +4202,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
@@ -4173,20 +4248,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4198,17 +4273,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
@@ -4223,20 +4298,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4248,7 +4323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4258,7 +4333,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -4273,7 +4348,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4283,7 +4358,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -4302,13 +4377,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -4327,13 +4402,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -4398,17 +4473,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -4423,7 +4498,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4433,7 +4508,7 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -4448,17 +4523,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -4473,20 +4548,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4498,20 +4573,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -4523,17 +4598,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -4548,7 +4623,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4573,17 +4648,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -4598,17 +4673,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -4623,7 +4698,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4633,7 +4708,7 @@
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
@@ -4648,7 +4723,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4658,7 +4733,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -4673,7 +4748,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4683,7 +4758,7 @@
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
@@ -4698,17 +4773,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -4723,7 +4798,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4733,7 +4808,7 @@
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
@@ -4748,7 +4823,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4758,7 +4833,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -4773,7 +4848,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4786,7 +4861,7 @@
         <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -4798,7 +4873,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4808,10 +4883,10 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -4823,20 +4898,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4848,17 +4923,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -4873,17 +4948,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F33" t="n">
         <v>3</v>
@@ -4898,17 +4973,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -4923,17 +4998,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -4948,17 +5023,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -4973,17 +5048,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -4998,17 +5073,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F38" t="n">
         <v>3</v>
@@ -5023,7 +5098,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5033,7 +5108,7 @@
         <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -5048,7 +5123,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5058,7 +5133,7 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -5073,17 +5148,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -5098,20 +5173,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -5123,7 +5198,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5133,10 +5208,10 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -5148,20 +5223,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -5173,17 +5248,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="F45" t="n">
         <v>2</v>
@@ -5198,17 +5273,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F46" t="n">
         <v>2</v>
@@ -5223,17 +5298,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -5248,17 +5323,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -5273,17 +5348,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -5298,17 +5373,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
@@ -5323,17 +5398,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
@@ -5348,17 +5423,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
@@ -5373,17 +5448,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
@@ -5398,17 +5473,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F54" t="n">
         <v>2</v>
@@ -5423,20 +5498,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -5448,20 +5523,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -5473,20 +5548,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -5498,17 +5573,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -5523,7 +5598,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5533,7 +5608,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -5548,17 +5623,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -5573,17 +5648,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -5598,17 +5673,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -5623,17 +5698,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -5648,7 +5723,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -5658,7 +5733,7 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -5673,17 +5748,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -5698,17 +5773,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -5723,22 +5798,72 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>Corbin Bosch</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>12</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>4</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
         <v>12</v>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>68.5</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,20 +572,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>68.5</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F7" t="n">
-        <v>61.33</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F8" t="n">
-        <v>59.67</v>
+        <v>61.33</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -647,20 +647,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="F9" t="n">
-        <v>59.5</v>
+        <v>59.67</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="F10" t="n">
-        <v>55.33</v>
+        <v>59.5</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>55.33</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="F12" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,13 +757,13 @@
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>51.67</v>
+        <v>54.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F14" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -797,20 +797,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>45.67</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="F17" t="n">
-        <v>45.67</v>
+        <v>46.25</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>224</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>44.8</v>
+        <v>45.67</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="F19" t="n">
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,13 +932,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>44.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -947,14 +947,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>176</v>
@@ -963,7 +963,7 @@
         <v>44</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -972,7 +972,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -982,13 +982,13 @@
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="F22" t="n">
         <v>44</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="F23" t="n">
-        <v>43.67</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="F24" t="n">
-        <v>42.6</v>
+        <v>43.67</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,13 +1057,13 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="F25" t="n">
-        <v>41.67</v>
+        <v>43.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>124</v>
+        <v>213</v>
       </c>
       <c r="F26" t="n">
-        <v>41.33</v>
+        <v>42.6</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>41.67</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1122,20 +1122,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>200</v>
+        <v>41</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>200</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,20 +1172,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="F30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="F34" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,14 +1297,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1313,7 +1313,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="F36" t="n">
-        <v>33.75</v>
+        <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="F37" t="n">
-        <v>33.5</v>
+        <v>33.75</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="F38" t="n">
-        <v>33.25</v>
+        <v>33.5</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F40" t="n">
-        <v>33</v>
+        <v>32.67</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1457,13 +1457,13 @@
         <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F41" t="n">
-        <v>32.67</v>
+        <v>31.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F42" t="n">
-        <v>31.75</v>
+        <v>31</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F43" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
         <v>2</v>
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F51" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>25.8</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F53" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
         <v>24</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="F57" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F59" t="n">
-        <v>19.67</v>
+        <v>21</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F60" t="n">
-        <v>19</v>
+        <v>19.67</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="F61" t="n">
-        <v>18.75</v>
+        <v>19</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2007,13 +2007,13 @@
         <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F63" t="n">
-        <v>18.67</v>
+        <v>18.75</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="F66" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="F67" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F68" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2157,10 +2157,10 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F69" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -2197,14 +2197,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
         <v>56</v>
@@ -2213,7 +2213,7 @@
         <v>14</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F72" t="n">
         <v>14</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F73" t="n">
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="F74" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F76" t="n">
         <v>12</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2372,11 +2372,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F79" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F80" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2463,7 +2463,7 @@
         <v>9</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,14 +2472,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>9</v>
@@ -2488,7 +2488,7 @@
         <v>9</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>4</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
         <v>9</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F84" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n">
-        <v>8.33</v>
+        <v>8.75</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F86" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F87" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
         <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F89" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="G90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -2772,14 +2772,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>5</v>
@@ -2788,7 +2788,7 @@
         <v>5</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -2797,23 +2797,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F95" t="n">
         <v>5</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
         <v>5</v>
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F97" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,11 +2872,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F99" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,11 +2922,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
         <v>1</v>
@@ -2938,7 +2938,7 @@
         <v>4</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2997,14 +2997,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
         <v>3</v>
@@ -3013,7 +3013,7 @@
         <v>3</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -3022,11 +3022,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -3038,7 +3038,7 @@
         <v>3</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F105" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,20 +3072,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
         <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3097,17 +3097,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F107" t="n">
         <v>2</v>
@@ -3122,20 +3122,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3147,14 +3147,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -3163,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>4</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3197,11 +3197,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3247,20 +3247,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -3347,14 +3347,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3397,14 +3397,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
@@ -4127,7 +4127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4208,10 +4208,10 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4223,20 +4223,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4323,11 +4323,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -4336,7 +4336,7 @@
         <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4358,7 +4358,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -4373,17 +4373,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4408,7 +4408,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -4423,17 +4423,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -4448,17 +4448,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -4473,17 +4473,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -4498,17 +4498,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -4523,17 +4523,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4558,7 +4558,7 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -4573,17 +4573,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -4598,20 +4598,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -4623,17 +4623,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -4648,17 +4648,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -4673,17 +4673,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -4698,17 +4698,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
@@ -4723,17 +4723,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4783,7 +4783,7 @@
         <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4808,7 +4808,7 @@
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4883,7 +4883,7 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4908,7 +4908,7 @@
         <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F31" t="n">
         <v>4</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -4936,7 +4936,7 @@
         <v>42</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4958,10 +4958,10 @@
         <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -4973,20 +4973,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
@@ -5023,17 +5023,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
@@ -5048,17 +5048,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -5073,17 +5073,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F38" t="n">
         <v>3</v>
@@ -5098,17 +5098,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5133,7 +5133,7 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -5173,17 +5173,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5208,7 +5208,7 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -5223,17 +5223,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -5248,20 +5248,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -5273,20 +5273,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -5298,17 +5298,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F47" t="n">
         <v>2</v>
@@ -5323,17 +5323,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -5348,17 +5348,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -5373,17 +5373,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5408,7 +5408,7 @@
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
@@ -5423,17 +5423,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
@@ -5448,17 +5448,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
@@ -5473,17 +5473,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F54" t="n">
         <v>2</v>
@@ -5498,17 +5498,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
@@ -5523,17 +5523,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5558,7 +5558,7 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -5573,20 +5573,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -5598,20 +5598,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -5698,17 +5698,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -5748,17 +5748,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -5773,17 +5773,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -5798,17 +5798,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -5848,22 +5848,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>4</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="n">
+      <c r="C70" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
         <v>12</v>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="F2" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>61.33</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>184</v>
+        <v>119</v>
       </c>
       <c r="F8" t="n">
-        <v>61.33</v>
+        <v>59.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -651,16 +651,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="F9" t="n">
-        <v>59.67</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>119</v>
+        <v>222</v>
       </c>
       <c r="F10" t="n">
-        <v>59.5</v>
+        <v>55.5</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>43.67</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1032,13 +1032,13 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
-        <v>43.67</v>
+        <v>43.5</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>87</v>
+        <v>213</v>
       </c>
       <c r="F25" t="n">
-        <v>43.5</v>
+        <v>42.6</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1082,13 +1082,13 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>213</v>
+        <v>127</v>
       </c>
       <c r="F26" t="n">
-        <v>42.6</v>
+        <v>42.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="F27" t="n">
-        <v>41.67</v>
+        <v>41</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1122,20 +1122,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="F28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1157,13 +1157,13 @@
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="F30" t="n">
         <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="F33" t="n">
-        <v>34.33</v>
+        <v>34.2</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="F34" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1297,14 +1297,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1313,7 +1313,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="F36" t="n">
-        <v>34</v>
+        <v>33.75</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1407,13 +1407,13 @@
         <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="F39" t="n">
-        <v>33</v>
+        <v>32.67</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,13 +1432,13 @@
         <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F40" t="n">
-        <v>32.67</v>
+        <v>31.75</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F41" t="n">
-        <v>31.75</v>
+        <v>31</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F42" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="F43" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>28.25</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="F45" t="n">
-        <v>28.25</v>
+        <v>27.8</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,10 +1607,10 @@
         <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F47" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="F48" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1647,11 +1647,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
         <v>2</v>
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F50" t="n">
         <v>26</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="F51" t="n">
         <v>26</v>
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F55" t="n">
         <v>24</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="F59" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="F60" t="n">
-        <v>19.67</v>
+        <v>22.6</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F61" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,13 +1982,13 @@
         <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>18.75</v>
+        <v>19.67</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,20 +1997,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="F63" t="n">
-        <v>18.75</v>
+        <v>19</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2022,17 +2022,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>18</v>
@@ -2047,17 +2047,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F65" t="n">
         <v>18</v>
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2107,13 +2107,13 @@
         <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F67" t="n">
-        <v>17.5</v>
+        <v>16.2</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2147,20 +2147,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F69" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F71" t="n">
         <v>14</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
         <v>14</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F73" t="n">
-        <v>14</v>
+        <v>12.6</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2282,13 +2282,13 @@
         <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>12.6</v>
+        <v>12.25</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2297,20 +2297,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F75" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F76" t="n">
         <v>12</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,20 +2347,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F77" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
         <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F80" t="n">
-        <v>10.25</v>
+        <v>9.5</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F86" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F88" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
         <v>6</v>
@@ -2738,7 +2738,7 @@
         <v>6</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F96" t="n">
         <v>5</v>
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4233,7 +4233,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
         <v>9</v>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4258,10 +4258,10 @@
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4273,20 +4273,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4298,20 +4298,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4323,20 +4323,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4348,20 +4348,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4373,20 +4373,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -4423,17 +4423,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4458,7 +4458,7 @@
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -4473,17 +4473,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4508,7 +4508,7 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -4523,17 +4523,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -4548,17 +4548,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4583,7 +4583,7 @@
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -4598,17 +4598,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -4623,20 +4623,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4648,20 +4648,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -4673,20 +4673,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -4748,17 +4748,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
@@ -4773,17 +4773,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4833,7 +4833,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -4848,17 +4848,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4883,7 +4883,7 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
@@ -4898,17 +4898,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F31" t="n">
         <v>4</v>
@@ -4923,17 +4923,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -4958,7 +4958,7 @@
         <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -4973,17 +4973,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -5011,7 +5011,7 @@
         <v>90</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -5023,20 +5023,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -5058,7 +5058,7 @@
         <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -5073,14 +5073,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>42</v>
@@ -5098,17 +5098,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -5123,17 +5123,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -5173,17 +5173,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -5223,17 +5223,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -5248,17 +5248,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
@@ -5273,17 +5273,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -5298,20 +5298,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -5323,20 +5323,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -5348,17 +5348,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -5373,17 +5373,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
@@ -5398,17 +5398,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="F51" t="n">
         <v>2</v>
@@ -5423,17 +5423,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F52" t="n">
         <v>2</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5458,7 +5458,7 @@
         <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
@@ -5473,17 +5473,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F54" t="n">
         <v>2</v>
@@ -5498,17 +5498,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
@@ -5523,17 +5523,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -5573,17 +5573,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -5598,17 +5598,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -5623,20 +5623,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -5673,17 +5673,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -522,20 +522,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -547,20 +547,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -572,20 +572,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="F6" t="n">
-        <v>68.5</v>
+        <v>70.33</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>61.33</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -622,20 +622,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="F8" t="n">
-        <v>59.5</v>
+        <v>67.67</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -657,13 +657,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>61.33</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,10 +682,10 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F10" t="n">
-        <v>55.5</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,20 +697,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="F11" t="n">
-        <v>55.33</v>
+        <v>55.5</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>55.33</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="F13" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>54.5</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>224</v>
+        <v>136</v>
       </c>
       <c r="F20" t="n">
-        <v>44.8</v>
+        <v>45.33</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,13 +957,13 @@
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>44.8</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -972,14 +972,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>176</v>
@@ -988,7 +988,7 @@
         <v>44</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,20 +997,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="F23" t="n">
-        <v>43.67</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="F32" t="n">
-        <v>34.33</v>
+        <v>34.2</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="F33" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1272,14 +1272,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
         <v>34</v>
@@ -1288,7 +1288,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="F35" t="n">
         <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1357,13 +1357,13 @@
         <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="F37" t="n">
-        <v>33.75</v>
+        <v>32.67</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="F38" t="n">
-        <v>33.5</v>
+        <v>31.75</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1397,20 +1397,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="F39" t="n">
-        <v>32.67</v>
+        <v>31</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
         <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F40" t="n">
-        <v>31.75</v>
+        <v>30.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F41" t="n">
-        <v>31</v>
+        <v>29.5</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="F42" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="F43" t="n">
-        <v>29</v>
+        <v>28.25</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="F44" t="n">
-        <v>28.25</v>
+        <v>27.8</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="F45" t="n">
-        <v>27.8</v>
+        <v>27.75</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F46" t="n">
-        <v>27.75</v>
+        <v>27.4</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F47" t="n">
-        <v>26.5</v>
+        <v>27.25</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1647,11 +1647,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
         <v>2</v>
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="F50" t="n">
         <v>26</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F51" t="n">
         <v>26</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1732,13 +1732,13 @@
         <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F52" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1747,20 +1747,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="F53" t="n">
-        <v>25</v>
+        <v>25.8</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F56" t="n">
         <v>24</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F57" t="n">
         <v>24</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="F58" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="F59" t="n">
         <v>23</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,10 +1932,10 @@
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F60" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="F61" t="n">
-        <v>21</v>
+        <v>22.6</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="F62" t="n">
-        <v>19.67</v>
+        <v>21.2</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F63" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2032,10 +2032,10 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F65" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="F66" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F67" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F68" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2157,10 +2157,10 @@
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F69" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F71" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,17 +2222,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F72" t="n">
         <v>14</v>
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="F73" t="n">
-        <v>12.6</v>
+        <v>14</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2272,20 +2272,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F74" t="n">
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="F75" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F77" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F79" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F80" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2457,10 +2457,10 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F81" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
         <v>9</v>
@@ -2522,17 +2522,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
         <v>9</v>
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2582,10 +2582,10 @@
         <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F86" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F87" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F91" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="G91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -2747,14 +2747,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
         <v>6</v>
@@ -2763,7 +2763,7 @@
         <v>6</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2838,7 +2838,7 @@
         <v>5</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F97" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>5</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E98" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F98" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2897,11 +2897,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
         <v>2</v>
@@ -2922,20 +2922,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F100" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -2947,11 +2947,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -2963,7 +2963,7 @@
         <v>4</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F102" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3022,14 +3022,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
         <v>3</v>
@@ -3038,7 +3038,7 @@
         <v>3</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -3063,7 +3063,7 @@
         <v>3</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3097,20 +3097,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
         <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3122,17 +3122,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F108" t="n">
         <v>2</v>
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3197,17 +3197,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -3222,11 +3222,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3247,11 +3247,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3272,11 +3272,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -3288,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3397,14 +3397,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3447,14 +3447,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3522,14 +3522,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D125" t="n">
         <v>0</v>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3647,14 +3647,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -3822,11 +3822,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3972,11 +3972,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -3997,14 +3997,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>5</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
@@ -4022,11 +4022,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -4097,22 +4097,72 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>3</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>5</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C147" t="n">
-        <v>4</v>
-      </c>
-      <c r="D147" t="n">
-        <v>0</v>
-      </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" t="n">
+      <c r="C149" t="n">
+        <v>5</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4398,20 +4448,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4423,17 +4473,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -4448,17 +4498,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -4473,17 +4523,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -4498,7 +4548,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4508,7 +4558,7 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -4523,17 +4573,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -4548,7 +4598,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4558,7 +4608,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -4573,7 +4623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4583,7 +4633,7 @@
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -4598,17 +4648,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -4623,17 +4673,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -4648,17 +4698,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
@@ -4673,17 +4723,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -4698,20 +4748,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4723,17 +4773,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -4748,17 +4798,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="F25" t="n">
         <v>4</v>
@@ -4773,17 +4823,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -4798,17 +4848,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
@@ -4823,7 +4873,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4848,7 +4898,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4873,7 +4923,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4883,7 +4933,7 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
@@ -4898,17 +4948,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F31" t="n">
         <v>4</v>
@@ -4927,13 +4977,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
@@ -4948,17 +4998,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -4973,17 +5023,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
@@ -4998,7 +5048,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -5008,7 +5058,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F35" t="n">
         <v>4</v>
@@ -5023,17 +5073,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
@@ -5048,7 +5098,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -5061,7 +5111,7 @@
         <v>90</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -5073,20 +5123,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -5098,7 +5148,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5108,7 +5158,7 @@
         <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F39" t="n">
         <v>3</v>
@@ -5123,7 +5173,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5133,7 +5183,7 @@
         <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -5148,17 +5198,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -5173,17 +5223,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -5198,17 +5248,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -5223,17 +5273,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -5248,17 +5298,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
         <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
@@ -5273,17 +5323,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -5298,17 +5348,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -5323,7 +5373,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -5333,7 +5383,7 @@
         <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
@@ -5348,20 +5398,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -5373,20 +5423,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -5398,20 +5448,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -5423,20 +5473,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -5448,17 +5498,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
@@ -5473,17 +5523,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F54" t="n">
         <v>2</v>
@@ -5498,7 +5548,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -5508,7 +5558,7 @@
         <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
@@ -5523,17 +5573,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -5548,17 +5598,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -5573,17 +5623,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -5723,17 +5773,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -5748,17 +5798,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -5773,17 +5823,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -5798,17 +5848,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
@@ -5823,17 +5873,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -532,10 +532,10 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -547,20 +547,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
-        <v>70.33</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>70.33</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>184</v>
+        <v>251</v>
       </c>
       <c r="F9" t="n">
-        <v>61.33</v>
+        <v>62.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,13 +682,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>61.33</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,10 +707,10 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F11" t="n">
-        <v>55.5</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="F12" t="n">
-        <v>55.33</v>
+        <v>55.5</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>55.33</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -897,20 +897,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="F19" t="n">
-        <v>45.5</v>
+        <v>45.33</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="F20" t="n">
-        <v>45.33</v>
+        <v>44.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,13 +957,13 @@
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="F21" t="n">
-        <v>44.8</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -972,20 +972,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>176</v>
+        <v>87</v>
       </c>
       <c r="F22" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -997,20 +997,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>42.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="F24" t="n">
-        <v>43.5</v>
+        <v>42.33</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>213</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
-        <v>42.6</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1082,13 +1082,13 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n">
-        <v>42.33</v>
+        <v>41</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>41</v>
+        <v>201</v>
       </c>
       <c r="F27" t="n">
-        <v>41</v>
+        <v>40.2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="F29" t="n">
         <v>38</v>
@@ -1247,14 +1247,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>34</v>
@@ -1263,7 +1263,7 @@
         <v>34</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1307,13 +1307,13 @@
         <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="F35" t="n">
-        <v>34</v>
+        <v>33.75</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,20 +1322,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
         <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F36" t="n">
-        <v>33.75</v>
+        <v>31.75</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>32.67</v>
+        <v>31</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -1372,20 +1372,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
         <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F38" t="n">
-        <v>31.75</v>
+        <v>30.5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1397,20 +1397,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="F39" t="n">
-        <v>31</v>
+        <v>30.4</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
         <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F40" t="n">
-        <v>30.5</v>
+        <v>29.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="F41" t="n">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>27.8</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,10 +1507,10 @@
         <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F43" t="n">
-        <v>28.25</v>
+        <v>27.75</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,13 +1532,13 @@
         <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="F44" t="n">
-        <v>27.8</v>
+        <v>27.75</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F45" t="n">
-        <v>27.75</v>
+        <v>27.4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1582,13 +1582,13 @@
         <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="F46" t="n">
-        <v>27.4</v>
+        <v>27.25</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,13 +1607,13 @@
         <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="F47" t="n">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="F48" t="n">
         <v>27</v>
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1672,11 +1672,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
         <v>2</v>
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="F51" t="n">
         <v>26</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="F55" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>24</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F57" t="n">
         <v>24</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="F58" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="F59" t="n">
         <v>23</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,10 +1932,10 @@
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F60" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="F61" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F63" t="n">
-        <v>21</v>
+        <v>20.33</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="F64" t="n">
-        <v>19</v>
+        <v>19.75</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2047,14 +2047,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
         <v>19</v>
@@ -2063,7 +2063,7 @@
         <v>19</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="F68" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2157,13 +2157,13 @@
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F69" t="n">
-        <v>16.2</v>
+        <v>17.5</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F70" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2232,13 +2232,13 @@
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F72" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2372,17 +2372,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F78" t="n">
         <v>12</v>
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F79" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F80" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,11 +2447,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F83" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2538,7 +2538,7 @@
         <v>9</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
         <v>9</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F86" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F88" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F89" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F90" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F92" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="G92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -2772,14 +2772,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
         <v>6</v>
@@ -2788,7 +2788,7 @@
         <v>6</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -2797,11 +2797,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -2851,16 +2851,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,20 +2872,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F98" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>5</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F99" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F100" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F101" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2997,20 +2997,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F103" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3022,20 +3022,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -3047,20 +3047,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3072,14 +3072,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>5</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
         <v>3</v>
@@ -3097,20 +3097,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3147,20 +3147,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
         <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3197,20 +3197,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3222,17 +3222,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -3247,11 +3247,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3272,11 +3272,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -3288,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -3313,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3372,11 +3372,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
@@ -3397,14 +3397,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3522,14 +3522,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -3697,14 +3697,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3772,14 +3772,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -3822,14 +3822,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -3947,11 +3947,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -3972,11 +3972,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -3997,14 +3997,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -4047,11 +4047,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -4072,11 +4072,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -4097,14 +4097,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -4147,22 +4147,47 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>5</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C149" t="n">
-        <v>5</v>
-      </c>
-      <c r="D149" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="n">
+      <c r="C150" t="n">
+        <v>5</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4177,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4227,16 +4252,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4398,20 +4423,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4427,16 +4452,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4448,7 +4473,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4458,7 +4483,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
@@ -4473,20 +4498,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -4498,20 +4523,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4523,20 +4548,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4548,17 +4573,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -4573,17 +4598,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -4598,17 +4623,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -4623,7 +4648,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4633,7 +4658,7 @@
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -4648,17 +4673,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -4673,17 +4698,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -4698,17 +4723,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
@@ -4723,17 +4748,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -4748,17 +4773,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
         <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -4773,20 +4798,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -4798,20 +4823,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4823,20 +4848,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -4848,7 +4873,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4873,17 +4898,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -4898,17 +4923,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
@@ -4923,17 +4948,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
@@ -4948,7 +4973,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4958,7 +4983,7 @@
         <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F31" t="n">
         <v>4</v>
@@ -4973,17 +4998,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
@@ -4998,17 +5023,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -5023,17 +5048,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
@@ -5048,7 +5073,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -5073,17 +5098,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
@@ -5098,17 +5123,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F37" t="n">
         <v>4</v>
@@ -5123,17 +5148,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
@@ -5148,20 +5173,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -5173,20 +5198,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -5198,17 +5223,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F41" t="n">
         <v>3</v>
@@ -5223,17 +5248,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
@@ -5248,17 +5273,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
@@ -5273,17 +5298,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -5298,17 +5323,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
@@ -5323,11 +5348,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>4</v>
@@ -5348,7 +5373,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5358,7 +5383,7 @@
         <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -5623,7 +5648,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5633,7 +5658,7 @@
         <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -5648,17 +5673,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -5673,17 +5698,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -5698,20 +5723,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -5723,17 +5748,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -5748,17 +5773,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -5773,17 +5798,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -5798,17 +5823,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -5823,7 +5848,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5833,7 +5858,7 @@
         <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -5848,17 +5873,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
@@ -5873,7 +5898,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5883,7 +5908,7 @@
         <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -5898,17 +5923,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -5923,22 +5948,72 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>Deepak Chahar</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>39</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>5</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="C72" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
         <v>12</v>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="F2" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>173</v>
+      </c>
+      <c r="F5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G5" t="n">
         <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>79</v>
-      </c>
-      <c r="F5" t="n">
-        <v>79</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>84.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>70.33</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,7 +622,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -632,10 +632,10 @@
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F8" t="n">
-        <v>67.67</v>
+        <v>70.33</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="F9" t="n">
-        <v>62.75</v>
+        <v>67.67</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>184</v>
+        <v>251</v>
       </c>
       <c r="F10" t="n">
-        <v>61.33</v>
+        <v>62.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,13 +707,13 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>61.33</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="F12" t="n">
-        <v>55.5</v>
+        <v>49.4</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,20 +747,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>166</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>55.33</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>109</v>
+        <v>283</v>
       </c>
       <c r="F14" t="n">
-        <v>54.5</v>
+        <v>47.17</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>102</v>
+        <v>230</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>45.67</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="F17" t="n">
-        <v>46.25</v>
+        <v>45.33</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="F18" t="n">
-        <v>45.67</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F19" t="n">
-        <v>45.33</v>
+        <v>42.33</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,13 +932,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="F20" t="n">
-        <v>44.8</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,13 +957,13 @@
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="F22" t="n">
-        <v>43.5</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -997,7 +997,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1007,10 +1007,10 @@
         <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F23" t="n">
-        <v>42.6</v>
+        <v>40.2</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1032,13 +1032,13 @@
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="F24" t="n">
-        <v>42.33</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="F26" t="n">
-        <v>41</v>
+        <v>38.4</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F27" t="n">
-        <v>40.2</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,20 +1122,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>35.5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>38</v>
+        <v>34.33</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="F31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="F32" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="F33" t="n">
-        <v>34</v>
+        <v>33.67</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="F34" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,20 +1297,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="F35" t="n">
-        <v>33.75</v>
+        <v>33.5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1322,20 +1322,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="F36" t="n">
-        <v>31.75</v>
+        <v>31.33</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
         <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="F37" t="n">
-        <v>31</v>
+        <v>30.6</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="F38" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="F39" t="n">
-        <v>30.4</v>
+        <v>29.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="F40" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1482,13 +1482,13 @@
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="F42" t="n">
-        <v>27.8</v>
+        <v>27.75</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F43" t="n">
-        <v>27.75</v>
+        <v>27.4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,10 +1532,10 @@
         <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F44" t="n">
-        <v>27.75</v>
+        <v>27.25</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F45" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1582,13 +1582,13 @@
         <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="F46" t="n">
-        <v>27.25</v>
+        <v>27</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1597,14 +1597,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
         <v>135</v>
@@ -1613,7 +1613,7 @@
         <v>27</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="F48" t="n">
         <v>27</v>
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="F50" t="n">
         <v>26</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="F51" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="F52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1757,10 +1757,10 @@
         <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F53" t="n">
-        <v>25.8</v>
+        <v>24</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="F55" t="n">
-        <v>24</v>
+        <v>23.83</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,10 +1857,10 @@
         <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F57" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="F58" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F59" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,10 +1932,10 @@
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F60" t="n">
-        <v>22.6</v>
+        <v>21.2</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="F61" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="F62" t="n">
-        <v>21.2</v>
+        <v>20.33</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,20 +1997,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="F63" t="n">
-        <v>20.33</v>
+        <v>19.75</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>19.75</v>
+        <v>19.5</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="F69" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F73" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2276,16 +2276,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F74" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -2301,16 +2301,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F75" t="n">
-        <v>12.6</v>
+        <v>13.67</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F77" t="n">
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
         <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F78" t="n">
         <v>12</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2397,17 +2397,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F79" t="n">
         <v>12</v>
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F80" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F81" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2472,11 +2472,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F83" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="F84" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>5</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F85" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -2572,17 +2572,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
         <v>9</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
         <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F87" t="n">
         <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F88" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2657,10 +2657,10 @@
         <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F89" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="F90" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
         <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2797,23 +2797,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F95" t="n">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2857,10 +2857,10 @@
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F97" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
         <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -2922,20 +2922,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F100" t="n">
-        <v>4.67</v>
+        <v>6</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F101" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F102" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F105" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,20 +3072,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>5</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>4.67</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -3097,20 +3097,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
         <v>4</v>
       </c>
-      <c r="D107" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" t="n">
-        <v>3</v>
-      </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3122,20 +3122,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -3147,20 +3147,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
         <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F109" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
         <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3197,20 +3197,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
         <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3247,20 +3247,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>5</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2</v>
+      </c>
+      <c r="E114" t="n">
         <v>4</v>
       </c>
-      <c r="D114" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" t="n">
-        <v>1</v>
-      </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -3313,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3322,14 +3322,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3338,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3347,23 +3347,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3397,11 +3397,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>5</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3572,14 +3572,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3672,11 +3672,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -3697,14 +3697,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3772,14 +3772,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -3847,14 +3847,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -3972,11 +3972,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C146" t="n">
         <v>5</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -4097,11 +4097,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -4172,22 +4172,72 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>4</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C150" t="n">
-        <v>5</v>
-      </c>
-      <c r="D150" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
+      <c r="C152" t="n">
+        <v>5</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4202,7 +4252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4248,20 +4298,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4273,7 +4323,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4283,10 +4333,10 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4298,20 +4348,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4323,7 +4373,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4333,7 +4383,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F5" t="n">
         <v>9</v>
@@ -4348,7 +4398,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4358,10 +4408,10 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4373,20 +4423,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4398,7 +4448,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4408,10 +4458,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4423,20 +4473,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4448,17 +4498,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F10" t="n">
         <v>7</v>
@@ -4473,7 +4523,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4483,10 +4533,10 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4498,7 +4548,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4508,10 +4558,10 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -4523,20 +4573,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4548,7 +4598,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4558,7 +4608,7 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
@@ -4573,20 +4623,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4598,20 +4648,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -4623,7 +4673,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4633,10 +4683,10 @@
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4648,17 +4698,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -4673,7 +4723,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4683,7 +4733,7 @@
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -4698,17 +4748,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -4723,7 +4773,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4748,17 +4798,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -4773,17 +4823,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
         <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -4798,7 +4848,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4808,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -4823,17 +4873,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
@@ -4848,7 +4898,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -4858,7 +4908,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -4873,20 +4923,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -4898,7 +4948,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4908,10 +4958,10 @@
         <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -4923,11 +4973,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
         <v>5</v>
@@ -4936,7 +4986,7 @@
         <v>114</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -4948,20 +4998,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -4973,20 +5023,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4998,20 +5048,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -5023,17 +5073,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -5048,17 +5098,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="F34" t="n">
         <v>4</v>
@@ -5073,17 +5123,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="F35" t="n">
         <v>4</v>
@@ -5098,17 +5148,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
         <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
@@ -5123,17 +5173,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="F37" t="n">
         <v>4</v>
@@ -5148,17 +5198,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
@@ -5173,17 +5223,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="F39" t="n">
         <v>4</v>
@@ -5198,17 +5248,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="F40" t="n">
         <v>4</v>
@@ -5223,20 +5273,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -5248,20 +5298,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -5273,7 +5323,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5283,10 +5333,10 @@
         <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -5298,7 +5348,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5308,7 +5358,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
@@ -5323,17 +5373,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
@@ -5348,17 +5398,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -5373,11 +5423,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
         <v>4</v>
@@ -5398,17 +5448,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F48" t="n">
         <v>3</v>
@@ -5423,7 +5473,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -5433,7 +5483,7 @@
         <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
@@ -5448,17 +5498,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -5473,7 +5523,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5483,7 +5533,7 @@
         <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -5498,17 +5548,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -5523,20 +5573,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -5548,17 +5598,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F54" t="n">
         <v>2</v>
@@ -5573,17 +5623,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
@@ -5598,17 +5648,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -5623,17 +5673,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -5648,17 +5698,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -5673,17 +5723,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -5698,17 +5748,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -5723,17 +5773,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -5748,20 +5798,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -5773,20 +5823,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -5798,17 +5848,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -5823,17 +5873,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -5848,17 +5898,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -5873,17 +5923,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
@@ -5898,7 +5948,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -5908,7 +5958,7 @@
         <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -5923,17 +5973,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -5948,17 +5998,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -5973,17 +6023,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -5998,22 +6048,47 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>5</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" t="n">
+      <c r="C73" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
         <v>12</v>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>173</v>
+      </c>
+      <c r="F4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G4" t="n">
         <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>97</v>
-      </c>
-      <c r="F4" t="n">
-        <v>97</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F5" t="n">
-        <v>86.5</v>
+        <v>84.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="F6" t="n">
-        <v>84.5</v>
+        <v>62.75</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -597,20 +597,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -622,20 +622,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F8" t="n">
-        <v>70.33</v>
+        <v>55.75</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="F9" t="n">
-        <v>67.67</v>
+        <v>55.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="F10" t="n">
-        <v>62.75</v>
+        <v>52.75</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="F11" t="n">
-        <v>61.33</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>49.33</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>283</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>47.17</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,7 +797,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -807,13 +807,13 @@
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>230</v>
+        <v>283</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>47.17</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="F16" t="n">
-        <v>45.67</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F17" t="n">
-        <v>45.33</v>
+        <v>45.67</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>42.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -897,7 +897,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -907,13 +907,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>127</v>
+        <v>211</v>
       </c>
       <c r="F19" t="n">
-        <v>42.33</v>
+        <v>42.2</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -997,20 +997,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>201</v>
+        <v>246</v>
       </c>
       <c r="F23" t="n">
-        <v>40.2</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1032,10 +1032,10 @@
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1107,10 +1107,10 @@
         <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>36.2</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
         <v>4</v>
       </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
+        <v>34.33</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,10 +1182,10 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F30" t="n">
-        <v>34.33</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="F31" t="n">
-        <v>34</v>
+        <v>33.67</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="F32" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,10 +1257,10 @@
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F33" t="n">
-        <v>33.67</v>
+        <v>33.5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="F34" t="n">
-        <v>33.6</v>
+        <v>33.33</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="F35" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1382,10 +1382,10 @@
         <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F38" t="n">
-        <v>30.4</v>
+        <v>29.4</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -1397,20 +1397,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="F39" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="F40" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>27.75</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1482,13 +1482,13 @@
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="F42" t="n">
-        <v>27.75</v>
+        <v>27.4</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,13 +1507,13 @@
         <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="F43" t="n">
-        <v>27.4</v>
+        <v>27.25</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="F44" t="n">
-        <v>27.25</v>
+        <v>27.2</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1557,13 +1557,13 @@
         <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="F45" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="F47" t="n">
         <v>27</v>
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>25.83</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="F51" t="n">
-        <v>25.6</v>
+        <v>25.67</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="F53" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="F54" t="n">
-        <v>24</v>
+        <v>25.33</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="F55" t="n">
-        <v>23.83</v>
+        <v>25</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="F56" t="n">
-        <v>23</v>
+        <v>24.67</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="F57" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="F59" t="n">
-        <v>22</v>
+        <v>23.83</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="F60" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="F61" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F62" t="n">
-        <v>20.33</v>
+        <v>20.5</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,20 +1997,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F63" t="n">
-        <v>19.75</v>
+        <v>20.33</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -2022,11 +2022,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
         <v>4</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F65" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2072,14 +2072,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v>19</v>
@@ -2088,7 +2088,7 @@
         <v>19</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F67" t="n">
         <v>19</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>12.25</v>
+        <v>13</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F77" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F78" t="n">
         <v>12</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D79" t="n">
         <v>3</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C87" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" t="n">
         <v>4</v>
       </c>
-      <c r="D87" t="n">
-        <v>3</v>
-      </c>
       <c r="E87" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F87" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F88" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F89" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2682,10 +2682,10 @@
         <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F90" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F91" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F92" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F93" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
         <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F95" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F96" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="G96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2847,14 +2847,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E97" t="n">
         <v>13</v>
@@ -2863,7 +2863,7 @@
         <v>6.5</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2897,14 +2897,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
         <v>6</v>
@@ -2913,7 +2913,7 @@
         <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -2922,11 +2922,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
         <v>1</v>
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F101" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2982,10 +2982,10 @@
         <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F102" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F103" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3022,11 +3022,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -3038,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F105" t="n">
         <v>5</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3072,20 +3072,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F106" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E107" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F107" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3122,11 +3122,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
@@ -3138,7 +3138,7 @@
         <v>4</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F109" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
         <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
@@ -3297,11 +3297,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
@@ -3322,11 +3322,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
@@ -3338,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3347,14 +3347,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -3363,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3422,11 +3422,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -3497,14 +3497,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3522,14 +3522,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3647,14 +3647,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -3847,14 +3847,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -3872,14 +3872,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -4022,11 +4022,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -4072,11 +4072,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
         <v>1</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -4097,14 +4097,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -4172,14 +4172,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>5</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,22 +4222,72 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>6</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v>5</v>
-      </c>
-      <c r="D152" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="n">
+      <c r="C154" t="n">
+        <v>6</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4252,7 +4302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4323,17 +4373,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F3" t="n">
         <v>11</v>
@@ -4348,20 +4398,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4373,20 +4423,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4402,16 +4452,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4423,7 +4473,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4448,17 +4498,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
@@ -4473,17 +4523,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
@@ -4498,7 +4548,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4508,10 +4558,10 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4523,20 +4573,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4548,7 +4598,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4558,7 +4608,7 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
         <v>7</v>
@@ -4573,17 +4623,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F13" t="n">
         <v>7</v>
@@ -4598,20 +4648,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4623,17 +4673,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
@@ -4648,17 +4698,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
@@ -4673,17 +4723,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
@@ -4698,20 +4748,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -4723,11 +4773,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
@@ -4736,7 +4786,7 @@
         <v>102</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -4748,20 +4798,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4773,20 +4823,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -4798,7 +4848,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4808,10 +4858,10 @@
         <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -4823,17 +4873,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -4848,17 +4898,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -4873,17 +4923,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
@@ -4898,17 +4948,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -4923,17 +4973,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -4948,7 +4998,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4973,7 +5023,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4983,7 +5033,7 @@
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -4998,17 +5048,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -5023,7 +5073,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -5033,7 +5083,7 @@
         <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -5048,17 +5098,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -5073,7 +5123,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -5083,10 +5133,10 @@
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -5098,7 +5148,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -5108,10 +5158,10 @@
         <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -5123,7 +5173,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -5133,10 +5183,10 @@
         <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -5148,20 +5198,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
         <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -5173,20 +5223,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -5198,17 +5248,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
@@ -5223,17 +5273,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F39" t="n">
         <v>4</v>
@@ -5248,17 +5298,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
         <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="F40" t="n">
         <v>4</v>
@@ -5273,17 +5323,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
@@ -5298,17 +5348,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F42" t="n">
         <v>4</v>
@@ -5323,17 +5373,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="F43" t="n">
         <v>4</v>
@@ -5348,20 +5398,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -5373,20 +5423,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -5398,20 +5448,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -5423,20 +5473,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>42</v>
+      </c>
+      <c r="F47" t="n">
         <v>4</v>
-      </c>
-      <c r="E47" t="n">
-        <v>96</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -5448,20 +5498,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -5473,17 +5523,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
@@ -5498,17 +5548,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
@@ -5523,7 +5573,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5533,7 +5583,7 @@
         <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -5548,17 +5598,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -5573,14 +5623,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
         <v>54</v>
@@ -5598,20 +5648,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -5623,20 +5673,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -5648,17 +5698,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
@@ -5673,17 +5723,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -5698,17 +5748,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
         <v>2</v>
@@ -5723,17 +5773,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -5748,17 +5798,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -5773,17 +5823,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -5798,17 +5848,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F62" t="n">
         <v>2</v>
@@ -5823,17 +5873,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F63" t="n">
         <v>2</v>
@@ -5848,20 +5898,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -5873,17 +5923,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -5973,17 +6023,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -5998,17 +6048,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -6023,17 +6073,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -6048,17 +6098,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -6073,22 +6123,47 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>7</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>36</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>6</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
+      <c r="C74" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
         <v>12</v>
       </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="n">
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F2" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>62.75</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>55.75</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -622,14 +622,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>223</v>
@@ -638,7 +638,7 @@
         <v>55.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="F9" t="n">
-        <v>55.75</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="F21" t="n">
         <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -972,7 +972,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -982,13 +982,13 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="F22" t="n">
         <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>246</v>
+        <v>39</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F24" t="n">
-        <v>40.2</v>
+        <v>38.4</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>181</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>36.2</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1082,13 +1082,13 @@
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="F26" t="n">
-        <v>38.4</v>
+        <v>35.5</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>36.2</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>213</v>
+        <v>103</v>
       </c>
       <c r="F28" t="n">
-        <v>35.5</v>
+        <v>34.33</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="F29" t="n">
         <v>34.33</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F30" t="n">
-        <v>34</v>
+        <v>34.33</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F37" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F38" t="n">
-        <v>29.4</v>
+        <v>30.6</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1397,14 +1397,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
         <v>147</v>
@@ -1413,7 +1413,7 @@
         <v>29.4</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="F40" t="n">
-        <v>29</v>
+        <v>29.4</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="F41" t="n">
-        <v>27.75</v>
+        <v>29</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F42" t="n">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,13 +1507,13 @@
         <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F43" t="n">
-        <v>27.25</v>
+        <v>27.4</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,10 +1532,10 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F44" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1557,13 +1557,13 @@
         <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="F45" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="F46" t="n">
         <v>27</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F48" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>25.83</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="F50" t="n">
-        <v>25.83</v>
+        <v>25.67</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="F51" t="n">
-        <v>25.67</v>
+        <v>25.6</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="F52" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="F53" t="n">
-        <v>25.5</v>
+        <v>25.33</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>25.33</v>
+        <v>25</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="F55" t="n">
-        <v>25</v>
+        <v>24.67</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1832,13 +1832,13 @@
         <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
-        <v>24.67</v>
+        <v>24.5</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F57" t="n">
         <v>24</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F58" t="n">
         <v>24</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="F60" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="F61" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="F62" t="n">
-        <v>20.5</v>
+        <v>20.17</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
         <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>20.33</v>
+        <v>19.5</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2022,11 +2022,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
         <v>4</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F65" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F66" t="n">
         <v>19</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F67" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F68" t="n">
         <v>18</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F69" t="n">
-        <v>18</v>
+        <v>16.75</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2272,20 +2272,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F74" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F75" t="n">
-        <v>13.67</v>
+        <v>13.75</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="F76" t="n">
-        <v>13</v>
+        <v>13.67</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,20 +2347,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F77" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>6</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F78" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>6</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F79" t="n">
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2422,17 +2422,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F80" t="n">
         <v>12</v>
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F81" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F82" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F84" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F85" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F86" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F87" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F88" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F89" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F90" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -3272,17 +3272,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F114" t="n">
         <v>2</v>
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3322,14 +3322,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3338,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3363,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -3388,7 +3388,7 @@
         <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3422,20 +3422,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3447,23 +3447,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3522,14 +3522,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -3572,14 +3572,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -3672,11 +3672,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3797,11 +3797,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,14 +3872,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
@@ -3897,14 +3897,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -3922,14 +3922,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -4022,11 +4022,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -4097,14 +4097,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C147" t="n">
         <v>6</v>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -4147,14 +4147,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4172,14 +4172,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,11 +4222,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -4272,22 +4272,97 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>5</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>6</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>6</v>
-      </c>
-      <c r="D154" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="n">
+      <c r="C157" t="n">
+        <v>6</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4302,7 +4377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4373,7 +4448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4383,10 +4458,10 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4398,17 +4473,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F4" t="n">
         <v>11</v>
@@ -4473,7 +4548,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4483,10 +4558,10 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4498,7 +4573,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4523,17 +4598,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
@@ -4548,17 +4623,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
@@ -4573,17 +4648,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -4598,20 +4673,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -4623,7 +4698,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4633,7 +4708,7 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
         <v>7</v>
@@ -4702,13 +4777,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
@@ -4723,7 +4798,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -4733,7 +4808,7 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
@@ -4748,7 +4823,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4758,7 +4833,7 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
@@ -4773,17 +4848,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
@@ -4798,17 +4873,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
@@ -4823,17 +4898,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F21" t="n">
         <v>6</v>
@@ -4848,17 +4923,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -4873,20 +4948,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4898,20 +4973,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -4923,17 +4998,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
@@ -4948,17 +5023,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -4973,17 +5048,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -4998,17 +5073,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -5023,17 +5098,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -5048,7 +5123,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5058,7 +5133,7 @@
         <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -5073,17 +5148,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -5098,7 +5173,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -5108,7 +5183,7 @@
         <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -5123,7 +5198,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -5133,7 +5208,7 @@
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F33" t="n">
         <v>5</v>
@@ -5148,7 +5223,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -5158,7 +5233,7 @@
         <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -5173,7 +5248,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -5198,7 +5273,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -5208,7 +5283,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -5223,17 +5298,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -5248,20 +5323,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -5273,17 +5348,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
         <v>4</v>
@@ -5298,17 +5373,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F40" t="n">
         <v>4</v>
@@ -5323,17 +5398,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
@@ -5348,7 +5423,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5358,7 +5433,7 @@
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F42" t="n">
         <v>4</v>
@@ -5373,17 +5448,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="F43" t="n">
         <v>4</v>
@@ -5398,17 +5473,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -5423,17 +5498,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -5448,7 +5523,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5458,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -5473,17 +5548,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
@@ -5498,17 +5573,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="F48" t="n">
         <v>4</v>
@@ -5523,20 +5598,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
         <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -5548,20 +5623,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -5573,17 +5648,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -5598,17 +5673,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -5623,7 +5698,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5633,7 +5708,7 @@
         <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -5648,17 +5723,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -5673,17 +5748,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
         <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -5698,20 +5773,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -5723,20 +5798,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -5748,20 +5823,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -5773,7 +5848,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5783,7 +5858,7 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -5798,17 +5873,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -5823,17 +5898,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -5848,17 +5923,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="F62" t="n">
         <v>2</v>
@@ -5873,17 +5948,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="F63" t="n">
         <v>2</v>
@@ -5898,17 +5973,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F64" t="n">
         <v>2</v>
@@ -5923,20 +5998,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -5948,17 +6023,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -5973,17 +6048,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
@@ -5998,17 +6073,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -6023,17 +6098,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -6048,7 +6123,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6058,7 +6133,7 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -6073,17 +6148,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -6098,7 +6173,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6108,7 +6183,7 @@
         <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -6123,17 +6198,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -6148,22 +6223,72 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>Deepak Chahar</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
+        <v>39</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>36</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>6</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
         <v>12</v>
       </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="n">
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>173</v>
+      </c>
+      <c r="F3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="G3" t="n">
         <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>101</v>
-      </c>
-      <c r="F3" t="n">
-        <v>101</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -532,13 +532,13 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F4" t="n">
-        <v>86.5</v>
+        <v>65.33</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>84.5</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>55.75</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -597,14 +597,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>223</v>
@@ -613,7 +613,7 @@
         <v>55.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>223</v>
+        <v>323</v>
       </c>
       <c r="F8" t="n">
-        <v>55.75</v>
+        <v>53.83</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>53.33</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="F10" t="n">
-        <v>52.75</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,10 +707,10 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>52.75</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="F12" t="n">
-        <v>49.4</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,20 +747,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="F13" t="n">
-        <v>49.33</v>
+        <v>50.5</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
@@ -772,20 +772,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>247</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -797,7 +797,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -807,13 +807,13 @@
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>283</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
-        <v>47.17</v>
+        <v>49.33</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>230</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="F17" t="n">
-        <v>45.67</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>42.5</v>
+        <v>45.67</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c r="F19" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,13 +932,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>41.8</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -972,7 +972,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -982,13 +982,13 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>246</v>
+        <v>123</v>
       </c>
       <c r="F22" t="n">
         <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>246</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,10 +1057,10 @@
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="F25" t="n">
-        <v>36.2</v>
+        <v>38.4</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1082,13 +1082,13 @@
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="F26" t="n">
-        <v>35.5</v>
+        <v>36.2</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,10 +1207,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F31" t="n">
-        <v>33.67</v>
+        <v>34.17</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="F32" t="n">
-        <v>33.6</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,10 +1257,10 @@
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F33" t="n">
-        <v>33.5</v>
+        <v>33.67</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F34" t="n">
-        <v>33.33</v>
+        <v>33.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="F35" t="n">
-        <v>33</v>
+        <v>33.33</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>188</v>
+        <v>132</v>
       </c>
       <c r="F36" t="n">
-        <v>31.33</v>
+        <v>33</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
         <v>6</v>
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="F50" t="n">
-        <v>25.67</v>
+        <v>25.71</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="F51" t="n">
-        <v>25.6</v>
+        <v>25.67</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1907,10 +1907,10 @@
         <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F59" t="n">
-        <v>23.83</v>
+        <v>22.67</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="F65" t="n">
-        <v>19</v>
+        <v>19.25</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="F70" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F71" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -2263,7 +2263,7 @@
         <v>14.4</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,20 +2272,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F74" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -2297,20 +2297,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F75" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F76" t="n">
-        <v>13.67</v>
+        <v>13.75</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="F77" t="n">
-        <v>13</v>
+        <v>13.67</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F78" t="n">
-        <v>12.2</v>
+        <v>13</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>6</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F79" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>6</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F80" t="n">
         <v>12</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2447,17 +2447,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F81" t="n">
         <v>12</v>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F83" t="n">
-        <v>11.5</v>
+        <v>11.67</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F84" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2547,11 +2547,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>6</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F86" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>10</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2657,13 +2657,13 @@
         <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F89" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E94" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F94" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
         <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F96" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
         <v>5</v>
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F111" t="n">
         <v>3</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3247,20 +3247,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F113" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3272,17 +3272,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F114" t="n">
         <v>2</v>
@@ -3297,20 +3297,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D115" t="n">
         <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F115" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
@@ -3672,11 +3672,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3797,11 +3797,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3822,14 +3822,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -3847,14 +3847,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -3947,11 +3947,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -4022,11 +4022,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C145" t="n">
         <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -4147,14 +4147,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -4172,14 +4172,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,11 +4222,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -4272,14 +4272,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>5</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4297,14 +4297,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -4322,11 +4322,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -4347,22 +4347,47 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C157" t="n">
-        <v>6</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="n">
+      <c r="C158" t="n">
+        <v>6</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4377,7 +4402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4448,17 +4473,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
@@ -4473,7 +4498,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4483,10 +4508,10 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4498,7 +4523,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4508,10 +4533,10 @@
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4523,7 +4548,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4533,7 +4558,7 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -4548,7 +4573,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4558,7 +4583,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -4573,7 +4598,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4583,10 +4608,10 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4598,7 +4623,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4608,7 +4633,7 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
@@ -4623,17 +4648,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
@@ -4648,17 +4673,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -4673,17 +4698,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
@@ -4698,7 +4723,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4708,10 +4733,10 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4723,17 +4748,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F14" t="n">
         <v>7</v>
@@ -4748,20 +4773,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4773,7 +4798,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4783,7 +4808,7 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
@@ -4798,17 +4823,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
@@ -4823,7 +4848,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4833,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
@@ -4848,17 +4873,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
@@ -4873,7 +4898,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4898,17 +4923,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F21" t="n">
         <v>6</v>
@@ -4923,17 +4948,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -4948,17 +4973,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
@@ -4973,17 +4998,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -4998,20 +5023,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -5023,20 +5048,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -5048,7 +5073,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5058,10 +5083,10 @@
         <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -5073,17 +5098,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -5098,17 +5123,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -5123,17 +5148,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -5173,17 +5198,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -5223,17 +5248,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -5248,17 +5273,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -5473,7 +5498,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5483,7 +5508,7 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -5498,17 +5523,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -5523,17 +5548,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -5548,14 +5573,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
         <v>102</v>
@@ -6098,17 +6123,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -6123,17 +6148,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -6148,17 +6173,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -6173,17 +6198,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -6198,17 +6223,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -6223,17 +6248,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
@@ -6248,17 +6273,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
         <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -6273,22 +6298,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>36</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>6</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
         <v>12</v>
       </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>55.75</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,14 +597,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>223</v>
@@ -613,7 +613,7 @@
         <v>55.75</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>49.33</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="F16" t="n">
         <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>211</v>
       </c>
       <c r="F19" t="n">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F20" t="n">
-        <v>42.2</v>
+        <v>41.8</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>209</v>
+        <v>123</v>
       </c>
       <c r="F21" t="n">
-        <v>41.8</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -972,20 +972,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>246</v>
+        <v>155</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>38.75</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>38.4</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="F25" t="n">
-        <v>38.4</v>
+        <v>36.29</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,20 +1072,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>36.2</v>
+        <v>35</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>34.33</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="F28" t="n">
         <v>34.33</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="F29" t="n">
         <v>34.33</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="F30" t="n">
-        <v>34.33</v>
+        <v>34.17</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="F31" t="n">
-        <v>34.17</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="F32" t="n">
-        <v>34</v>
+        <v>33.67</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,10 +1257,10 @@
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F33" t="n">
-        <v>33.67</v>
+        <v>33.5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F34" t="n">
-        <v>33.5</v>
+        <v>33.33</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="F35" t="n">
-        <v>33.33</v>
+        <v>33</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="F36" t="n">
-        <v>33</v>
+        <v>30.8</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F37" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="F38" t="n">
-        <v>30.6</v>
+        <v>30.17</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="F39" t="n">
-        <v>29.4</v>
+        <v>30</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1572,14 +1572,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
         <v>162</v>
@@ -1588,7 +1588,7 @@
         <v>27</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="F47" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="F48" t="n">
-        <v>26</v>
+        <v>25.71</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="F49" t="n">
-        <v>25.83</v>
+        <v>25.5</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1682,13 +1682,13 @@
         <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F50" t="n">
-        <v>25.71</v>
+        <v>25.33</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F51" t="n">
-        <v>25.67</v>
+        <v>25</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>6</v>
       </c>
       <c r="D52" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="n">
+        <v>49</v>
+      </c>
+      <c r="F52" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G52" t="n">
         <v>4</v>
-      </c>
-      <c r="E52" t="n">
-        <v>51</v>
-      </c>
-      <c r="F52" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1757,10 +1757,10 @@
         <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F53" t="n">
-        <v>25.33</v>
+        <v>24.5</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="F54" t="n">
-        <v>25</v>
+        <v>24.25</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="F55" t="n">
-        <v>24.67</v>
+        <v>24</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="G56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="F57" t="n">
-        <v>24</v>
+        <v>23.14</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="F58" t="n">
-        <v>24</v>
+        <v>22.67</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1907,10 +1907,10 @@
         <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F59" t="n">
-        <v>22.67</v>
+        <v>22.5</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E60" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F60" t="n">
-        <v>22.5</v>
+        <v>21.14</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2107,13 +2107,13 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F68" t="n">
         <v>18</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F69" t="n">
-        <v>16.75</v>
+        <v>18</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="F70" t="n">
-        <v>16.5</v>
+        <v>16.75</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="F71" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F72" t="n">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="F73" t="n">
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2272,20 +2272,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F74" t="n">
-        <v>14.4</v>
+        <v>15.25</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -2297,20 +2297,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
         <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F76" t="n">
-        <v>13.75</v>
+        <v>14.4</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D77" t="n">
         <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F77" t="n">
-        <v>13.67</v>
+        <v>14.4</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>6</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F79" t="n">
-        <v>12.2</v>
+        <v>13.75</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>6</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="F80" t="n">
-        <v>12</v>
+        <v>13.67</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E81" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F81" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,14 +2472,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
         <v>12</v>
@@ -2488,7 +2488,7 @@
         <v>12</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F83" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F84" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F86" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>6</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E89" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>10.43</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>6</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F92" t="n">
-        <v>8.33</v>
+        <v>10</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F93" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F94" t="n">
-        <v>7.75</v>
+        <v>8.33</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F96" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="G97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2872,20 +2872,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F98" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2947,14 +2947,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" t="n">
         <v>6</v>
@@ -2963,7 +2963,7 @@
         <v>6</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F102" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -3022,20 +3022,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F104" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -3047,20 +3047,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F105" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3072,17 +3072,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>6</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F106" t="n">
         <v>5</v>
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F107" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3122,20 +3122,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3147,20 +3147,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F110" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -3247,20 +3247,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
         <v>3</v>
       </c>
       <c r="F115" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3347,23 +3347,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>6</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -3438,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3447,14 +3447,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -3463,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -3497,20 +3497,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -3622,14 +3622,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -3647,14 +3647,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3797,11 +3797,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3822,11 +3822,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -3847,14 +3847,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3897,14 +3897,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -3922,14 +3922,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3972,11 +3972,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -3997,14 +3997,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -4047,11 +4047,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -4072,14 +4072,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -4097,11 +4097,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -4172,14 +4172,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,14 +4222,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C152" t="n">
         <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4247,14 +4247,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -4272,11 +4272,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -4297,14 +4297,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>5</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -4322,11 +4322,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4372,22 +4372,72 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>6</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>6</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
+      <c r="C160" t="n">
+        <v>6</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4448,17 +4498,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F2" t="n">
         <v>13</v>
@@ -4473,20 +4523,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4498,17 +4548,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F4" t="n">
         <v>12</v>
@@ -4523,7 +4573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4533,10 +4583,10 @@
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4548,20 +4598,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4577,16 +4627,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4598,7 +4648,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4608,7 +4658,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -4623,7 +4673,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4633,10 +4683,10 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4648,7 +4698,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4658,7 +4708,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
@@ -4673,17 +4723,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -4698,17 +4748,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
@@ -4723,17 +4773,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
@@ -4748,20 +4798,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4773,17 +4823,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="F15" t="n">
         <v>7</v>
@@ -4798,7 +4848,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4808,10 +4858,10 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -4823,20 +4873,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -4848,17 +4898,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
@@ -4873,7 +4923,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4883,7 +4933,7 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
@@ -4898,17 +4948,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
@@ -4923,7 +4973,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4933,7 +4983,7 @@
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="F21" t="n">
         <v>6</v>
@@ -4948,17 +4998,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -4973,7 +5023,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4998,17 +5048,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -5023,7 +5073,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5033,7 +5083,7 @@
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
@@ -5048,17 +5098,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
@@ -5073,17 +5123,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="F27" t="n">
         <v>6</v>
@@ -5098,20 +5148,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -5123,20 +5173,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -5148,17 +5198,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -5173,17 +5223,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -5198,14 +5248,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
         <v>120</v>
@@ -5223,17 +5273,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="F33" t="n">
         <v>5</v>
@@ -5248,17 +5298,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -5273,7 +5323,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -5283,7 +5333,7 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -5298,17 +5348,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -5323,7 +5373,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -5333,7 +5383,7 @@
         <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -5348,17 +5398,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="F38" t="n">
         <v>5</v>
@@ -5373,20 +5423,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -5398,17 +5448,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F40" t="n">
         <v>4</v>
@@ -5423,7 +5473,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5433,7 +5483,7 @@
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
@@ -5448,17 +5498,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="F42" t="n">
         <v>4</v>
@@ -5473,17 +5523,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F43" t="n">
         <v>4</v>
@@ -5498,17 +5548,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -5523,17 +5573,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -5548,17 +5598,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -5573,17 +5623,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
@@ -5598,17 +5648,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="F48" t="n">
         <v>4</v>
@@ -5623,17 +5673,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F49" t="n">
         <v>4</v>
@@ -5648,17 +5698,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="F50" t="n">
         <v>4</v>
@@ -5673,20 +5723,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -5698,20 +5748,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -5723,17 +5773,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
@@ -5748,17 +5798,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -5773,7 +5823,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -5783,7 +5833,7 @@
         <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -5798,17 +5848,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -5823,7 +5873,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5833,7 +5883,7 @@
         <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -5848,17 +5898,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -5873,20 +5923,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -5927,7 +5977,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
         <v>3</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>86.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="F3" t="n">
-        <v>86.5</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="F7" t="n">
-        <v>55.75</v>
+        <v>58.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,20 +622,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>323</v>
+        <v>223</v>
       </c>
       <c r="F8" t="n">
-        <v>53.83</v>
+        <v>55.75</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -657,10 +657,10 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F9" t="n">
-        <v>53.33</v>
+        <v>53.83</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>53.33</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="F11" t="n">
-        <v>52.75</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -722,7 +722,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -732,10 +732,10 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>52.75</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,7 +747,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -757,13 +757,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>101</v>
+        <v>208</v>
       </c>
       <c r="F13" t="n">
-        <v>50.5</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>247</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -797,20 +797,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>247</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>245</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
         <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="F18" t="n">
-        <v>45.67</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="F19" t="n">
-        <v>42.2</v>
+        <v>45.67</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F20" t="n">
-        <v>41.8</v>
+        <v>42.2</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>41.8</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="F24" t="n">
-        <v>38.4</v>
+        <v>36.29</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>254</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
-        <v>36.29</v>
+        <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>34.33</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="F27" t="n">
-        <v>34.33</v>
+        <v>34.17</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1122,20 +1122,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="F28" t="n">
-        <v>34.33</v>
+        <v>34</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>103</v>
+        <v>202</v>
       </c>
       <c r="F29" t="n">
-        <v>34.33</v>
+        <v>33.67</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,10 +1182,10 @@
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F30" t="n">
-        <v>34.17</v>
+        <v>33.5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,13 +1207,13 @@
         <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>238</v>
+        <v>200</v>
       </c>
       <c r="F31" t="n">
-        <v>34</v>
+        <v>33.33</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="F32" t="n">
-        <v>33.67</v>
+        <v>33</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="F33" t="n">
-        <v>33.5</v>
+        <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="F34" t="n">
-        <v>33.33</v>
+        <v>30.6</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="F35" t="n">
-        <v>33</v>
+        <v>30.17</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,20 +1322,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="F36" t="n">
-        <v>30.8</v>
+        <v>30.17</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="F37" t="n">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1372,20 +1372,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="F38" t="n">
-        <v>30.17</v>
+        <v>29.5</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>210</v>
+        <v>29</v>
       </c>
       <c r="F39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
         <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F40" t="n">
-        <v>29.4</v>
+        <v>27.4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>27.4</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -1472,20 +1472,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
         <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F42" t="n">
-        <v>28.8</v>
+        <v>27.2</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="F43" t="n">
-        <v>27.4</v>
+        <v>27</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="F44" t="n">
-        <v>27.4</v>
+        <v>26.83</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>136</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="F46" t="n">
-        <v>27</v>
+        <v>25.75</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="F47" t="n">
-        <v>26</v>
+        <v>25.71</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1632,13 +1632,13 @@
         <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="F48" t="n">
-        <v>25.71</v>
+        <v>25.67</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="F55" t="n">
         <v>24</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="F56" t="n">
-        <v>24</v>
+        <v>23.14</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,20 +1847,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E57" t="n">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="F57" t="n">
-        <v>23.14</v>
+        <v>22.67</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,10 +1882,10 @@
         <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F58" t="n">
-        <v>22.67</v>
+        <v>22.5</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E59" t="n">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="F59" t="n">
-        <v>22.5</v>
+        <v>22.43</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1951,16 +1951,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="F61" t="n">
-        <v>20.5</v>
+        <v>20.67</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="F62" t="n">
-        <v>20.17</v>
+        <v>19.5</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1997,11 +1997,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
         <v>4</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="F64" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E76" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="F76" t="n">
-        <v>14.4</v>
+        <v>14.86</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2347,14 +2347,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
         <v>72</v>
@@ -2363,7 +2363,7 @@
         <v>14.4</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F78" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>6</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F79" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>6</v>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="F80" t="n">
-        <v>13.67</v>
+        <v>13.75</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="F89" t="n">
-        <v>10.43</v>
+        <v>10.75</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E90" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F90" t="n">
-        <v>10.4</v>
+        <v>10.43</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>6</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="F91" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
         <v>10</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
-        <v>8.33</v>
+        <v>9.5</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2797,23 +2797,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F95" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F97" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F98" t="n">
         <v>7</v>
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F99" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2922,20 +2922,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F100" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E101" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F101" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F102" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2997,14 +2997,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
         <v>6</v>
@@ -3013,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3022,20 +3022,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F104" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F105" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,20 +3072,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F106" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -3097,20 +3097,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F107" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F109" t="n">
         <v>5</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3172,17 +3172,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F110" t="n">
         <v>5</v>
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3222,11 +3222,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
@@ -3238,7 +3238,7 @@
         <v>4</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3247,23 +3247,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F113" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F115" t="n">
         <v>3</v>
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3347,14 +3347,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>2</v>
@@ -3363,7 +3363,7 @@
         <v>2</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D118" t="n">
         <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F118" t="n">
         <v>2</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -3397,20 +3397,20 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
         <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3432,13 +3432,13 @@
         <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3447,14 +3447,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -3463,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
@@ -3497,11 +3497,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
@@ -3513,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -3572,20 +3572,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3622,14 +3622,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3797,11 +3797,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4508,10 +4508,10 @@
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4523,17 +4523,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F3" t="n">
         <v>13</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4711,7 +4711,7 @@
         <v>102</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4723,17 +4723,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
         <v>8</v>
@@ -4748,17 +4748,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
@@ -4773,17 +4773,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4808,7 +4808,7 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
@@ -4823,20 +4823,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4848,17 +4848,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
@@ -4873,17 +4873,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F17" t="n">
         <v>7</v>
@@ -4898,20 +4898,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -4923,17 +4923,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
         <v>6</v>
@@ -4948,17 +4948,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
@@ -4973,17 +4973,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
         <v>6</v>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5033,7 +5033,7 @@
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
@@ -5048,17 +5048,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5098,17 +5098,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5133,7 +5133,7 @@
         <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F27" t="n">
         <v>6</v>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F28" t="n">
         <v>6</v>
@@ -5173,17 +5173,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="F29" t="n">
         <v>6</v>
@@ -5198,20 +5198,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -5223,20 +5223,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -5248,17 +5248,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -5273,17 +5273,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="F33" t="n">
         <v>5</v>
@@ -5298,17 +5298,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -5323,17 +5323,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -5358,7 +5358,7 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -5373,17 +5373,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -5408,7 +5408,7 @@
         <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F38" t="n">
         <v>5</v>
@@ -5423,17 +5423,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="F39" t="n">
         <v>5</v>
@@ -5448,20 +5448,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -5473,20 +5473,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -5498,20 +5498,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -5523,20 +5523,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -5573,17 +5573,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -5598,17 +5598,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F48" t="n">
         <v>4</v>
@@ -5673,14 +5673,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
         <v>102</v>
@@ -5698,17 +5698,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="F50" t="n">
         <v>4</v>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="F51" t="n">
         <v>4</v>
@@ -5748,17 +5748,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F52" t="n">
         <v>4</v>
@@ -5773,20 +5773,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -5798,17 +5798,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -5848,17 +5848,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -5898,17 +5898,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -5923,14 +5923,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
         <v>54</v>
@@ -5948,20 +5948,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -5973,20 +5973,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -5998,20 +5998,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="F63" t="n">
         <v>2</v>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="F64" t="n">
         <v>2</v>
@@ -6073,17 +6073,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F65" t="n">
         <v>2</v>
@@ -6098,20 +6098,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -6133,10 +6133,10 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -6148,17 +6148,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="F2" t="n">
-        <v>86.5</v>
+        <v>91.5</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -657,10 +657,10 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F9" t="n">
-        <v>53.83</v>
+        <v>54.67</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,10 +682,10 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F10" t="n">
-        <v>53.33</v>
+        <v>53.83</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>53.33</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -797,7 +797,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -807,13 +807,13 @@
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="F15" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>230</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>45.67</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="F19" t="n">
-        <v>45.67</v>
+        <v>42.2</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F20" t="n">
-        <v>42.2</v>
+        <v>41.8</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,20 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="F21" t="n">
-        <v>41.8</v>
+        <v>39.67</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -1072,20 +1072,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F26" t="n">
-        <v>34.33</v>
+        <v>34.67</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1172,20 +1172,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="F30" t="n">
-        <v>33.5</v>
+        <v>33.57</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F31" t="n">
-        <v>33.33</v>
+        <v>33.5</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="F32" t="n">
-        <v>33</v>
+        <v>33.33</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,13 +1257,13 @@
         <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="F33" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="F34" t="n">
-        <v>30.6</v>
+        <v>33</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1307,13 +1307,13 @@
         <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="F35" t="n">
-        <v>30.17</v>
+        <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1332,13 +1332,13 @@
         <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F36" t="n">
-        <v>30.17</v>
+        <v>31.2</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1357,13 +1357,13 @@
         <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>30.17</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,20 +1372,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="F38" t="n">
-        <v>29.5</v>
+        <v>30.17</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>29</v>
+        <v>210</v>
       </c>
       <c r="F39" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
         <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F40" t="n">
-        <v>27.4</v>
+        <v>29.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="F41" t="n">
-        <v>27.4</v>
+        <v>29</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F42" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="F43" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" t="n">
-        <v>26.83</v>
+        <v>27</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>26.83</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="F46" t="n">
-        <v>25.75</v>
+        <v>26</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="F47" t="n">
-        <v>25.71</v>
+        <v>25.75</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1632,13 +1632,13 @@
         <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="F48" t="n">
-        <v>25.67</v>
+        <v>25.71</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="F49" t="n">
-        <v>25.5</v>
+        <v>25.67</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="F50" t="n">
-        <v>25.33</v>
+        <v>25.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="F51" t="n">
-        <v>25</v>
+        <v>25.33</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F52" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="F53" t="n">
         <v>24.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="F54" t="n">
-        <v>24.25</v>
+        <v>24.5</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,13 +1807,13 @@
         <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="F55" t="n">
-        <v>24</v>
+        <v>24.25</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
-        <v>23.14</v>
+        <v>24</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1847,20 +1847,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="F57" t="n">
-        <v>22.67</v>
+        <v>23.14</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="F58" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F59" t="n">
-        <v>22.43</v>
+        <v>22.67</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,10 +1932,10 @@
         <v>7</v>
       </c>
       <c r="E60" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F60" t="n">
-        <v>21.14</v>
+        <v>22.43</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="F61" t="n">
-        <v>20.67</v>
+        <v>21.14</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F62" t="n">
-        <v>19.5</v>
+        <v>20.67</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,11 +1997,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
         <v>4</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="F65" t="n">
-        <v>19.25</v>
+        <v>19.4</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F66" t="n">
-        <v>19</v>
+        <v>19.25</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F67" t="n">
         <v>19</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2132,13 +2132,13 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2147,14 +2147,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
         <v>36</v>
@@ -2163,7 +2163,7 @@
         <v>18</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F70" t="n">
-        <v>16.75</v>
+        <v>18</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2207,10 +2207,10 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F72" t="n">
-        <v>16.2</v>
+        <v>16.75</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2257,13 +2257,13 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F73" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
         <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="F74" t="n">
-        <v>15.25</v>
+        <v>16.2</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2297,20 +2297,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="F76" t="n">
-        <v>14.86</v>
+        <v>15.25</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>7</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E78" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="F78" t="n">
-        <v>14.4</v>
+        <v>14.86</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F79" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F80" t="n">
-        <v>13.75</v>
+        <v>14.4</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="F81" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F82" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F83" t="n">
-        <v>12</v>
+        <v>13.75</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F84" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F85" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F86" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F88" t="n">
-        <v>11</v>
+        <v>11.67</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F89" t="n">
-        <v>10.75</v>
+        <v>11.5</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
-        <v>10.43</v>
+        <v>11</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>6</v>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F92" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E93" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="F93" t="n">
-        <v>10</v>
+        <v>10.43</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E94" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F94" t="n">
-        <v>9.5</v>
+        <v>10.33</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>6</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F95" t="n">
-        <v>7.75</v>
+        <v>10</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E96" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F96" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F97" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E98" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F98" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F100" t="n">
         <v>7</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F101" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2982,10 +2982,10 @@
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F102" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D103" t="n">
         <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F104" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3047,14 +3047,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
         <v>6</v>
@@ -3063,7 +3063,7 @@
         <v>6</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -3072,20 +3072,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F106" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F107" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3147,20 +3147,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F109" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F110" t="n">
         <v>5</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F111" t="n">
         <v>5</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E112" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3247,20 +3247,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E113" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
@@ -3272,20 +3272,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F114" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3297,20 +3297,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3347,20 +3347,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F119" t="n">
         <v>2</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3422,23 +3422,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D120" t="n">
         <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3447,23 +3447,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D121" t="n">
         <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
         <v>1</v>
@@ -3513,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
@@ -3572,17 +3572,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -3597,14 +3597,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
         <v>1</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -3622,20 +3622,20 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3647,23 +3647,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3797,11 +3797,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D135" t="n">
         <v>0</v>
@@ -3822,11 +3822,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3897,14 +3897,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3997,14 +3997,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -4097,14 +4097,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C148" t="n">
         <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -4172,11 +4172,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4222,14 +4222,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -4247,14 +4247,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>7</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -4272,11 +4272,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -4297,14 +4297,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,22 +4422,97 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>5</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>6</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C160" t="n">
-        <v>6</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" t="n">
+      <c r="C163" t="n">
+        <v>6</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4452,7 +4527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4577,13 +4652,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F5" t="n">
         <v>12</v>
@@ -4623,7 +4698,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4633,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
@@ -4648,20 +4723,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4677,13 +4752,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -4748,7 +4823,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4758,7 +4833,7 @@
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
@@ -4773,17 +4848,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
@@ -4823,17 +4898,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F15" t="n">
         <v>8</v>
@@ -4848,20 +4923,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -4873,17 +4948,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="F17" t="n">
         <v>7</v>
@@ -4898,17 +4973,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F18" t="n">
         <v>7</v>
@@ -4923,20 +4998,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -4948,20 +5023,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4973,17 +5048,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F21" t="n">
         <v>6</v>
@@ -4998,17 +5073,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
@@ -5023,17 +5098,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
@@ -5048,17 +5123,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -5073,7 +5148,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5083,7 +5158,7 @@
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
@@ -5302,13 +5377,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -5398,17 +5473,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="F38" t="n">
         <v>5</v>
@@ -5423,17 +5498,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F39" t="n">
         <v>5</v>
@@ -5448,7 +5523,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5458,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
@@ -5473,17 +5548,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="F41" t="n">
         <v>5</v>
@@ -5498,7 +5573,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5508,7 +5583,7 @@
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
@@ -5523,17 +5598,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
@@ -5548,20 +5623,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -5573,7 +5648,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5583,7 +5658,7 @@
         <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -5598,17 +5673,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
@@ -5623,17 +5698,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
@@ -5648,17 +5723,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="F48" t="n">
         <v>4</v>
@@ -5673,17 +5748,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F49" t="n">
         <v>4</v>
@@ -5698,14 +5773,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
         <v>102</v>
@@ -5723,17 +5798,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="F51" t="n">
         <v>4</v>
@@ -5748,17 +5823,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="F52" t="n">
         <v>4</v>
@@ -5773,17 +5848,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
         <v>4</v>
@@ -5798,20 +5873,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -5823,17 +5898,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
@@ -6002,13 +6077,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -6198,17 +6273,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -6223,17 +6298,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -6248,17 +6323,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>7</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -6273,7 +6348,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6283,7 +6358,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -6298,17 +6373,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
@@ -6323,7 +6398,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6333,7 +6408,7 @@
         <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -6348,17 +6423,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
@@ -6373,22 +6448,72 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>Deepak Chahar</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>39</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cameron Green</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>36</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>Shivam Dube</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>7</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
         <v>12</v>
       </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="n">
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>279</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>69.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="F4" t="n">
-        <v>65.33</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>65.33</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -597,20 +597,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>293</v>
+        <v>120</v>
       </c>
       <c r="F7" t="n">
-        <v>58.6</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -622,20 +622,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>223</v>
+        <v>357</v>
       </c>
       <c r="F8" t="n">
-        <v>55.75</v>
+        <v>59.5</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -657,13 +657,13 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="F9" t="n">
-        <v>54.67</v>
+        <v>58.6</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="F10" t="n">
-        <v>53.83</v>
+        <v>57.4</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,10 +707,10 @@
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F11" t="n">
-        <v>53.33</v>
+        <v>54.67</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>211</v>
+        <v>380</v>
       </c>
       <c r="F12" t="n">
-        <v>52.75</v>
+        <v>54.29</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="F13" t="n">
         <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>349</v>
       </c>
       <c r="F14" t="n">
-        <v>50.5</v>
+        <v>49.86</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -897,20 +897,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>211</v>
+        <v>357</v>
       </c>
       <c r="F19" t="n">
-        <v>42.2</v>
+        <v>44.62</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="F20" t="n">
-        <v>41.8</v>
+        <v>42.5</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="F21" t="n">
-        <v>39.67</v>
+        <v>42.33</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>209</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>41.8</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,7 +997,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1007,13 +1007,13 @@
         <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="F23" t="n">
-        <v>38.75</v>
+        <v>39.67</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>254</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>36.29</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="F26" t="n">
-        <v>34.67</v>
+        <v>38.75</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>205</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>34.17</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>238</v>
+        <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1147,20 +1147,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F29" t="n">
-        <v>33.67</v>
+        <v>34.67</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1172,20 +1172,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="F30" t="n">
-        <v>33.57</v>
+        <v>33.67</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="F31" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1232,13 +1232,13 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="F32" t="n">
-        <v>33.33</v>
+        <v>33.57</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="F33" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="F34" t="n">
-        <v>33</v>
+        <v>33.33</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>128</v>
+        <v>232</v>
       </c>
       <c r="F35" t="n">
-        <v>32</v>
+        <v>33.14</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1332,13 +1332,13 @@
         <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="F36" t="n">
-        <v>31.2</v>
+        <v>33</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="F37" t="n">
-        <v>30.17</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1382,13 +1382,13 @@
         <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="F38" t="n">
-        <v>30.17</v>
+        <v>32</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1407,13 +1407,13 @@
         <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="F39" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="F40" t="n">
-        <v>29.5</v>
+        <v>30.17</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>29</v>
+        <v>210</v>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F42" t="n">
-        <v>27.4</v>
+        <v>29.5</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="F43" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
         <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F44" t="n">
-        <v>27</v>
+        <v>28.67</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="F45" t="n">
-        <v>26.83</v>
+        <v>27.4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="F46" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,13 +1607,13 @@
         <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="F47" t="n">
-        <v>25.75</v>
+        <v>26.83</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1622,20 +1622,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="F48" t="n">
-        <v>25.71</v>
+        <v>26</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
-        <v>25.67</v>
+        <v>26</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>7</v>
     